--- a/docs/xlsx/jobs-2026-08-26.xlsx
+++ b/docs/xlsx/jobs-2026-08-26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="956">
   <si>
     <t>Title</t>
   </si>
@@ -412,6 +412,24 @@
     <t>https://www.conservationjobboard.com/job-listing-gamebird-production-manager-commerce-texas/1859314324</t>
   </si>
   <si>
+    <t>Graduate Fellow in Environmental Education and Science Communication</t>
+  </si>
+  <si>
+    <t>University of Idaho</t>
+  </si>
+  <si>
+    <t>McCall, ID</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>$1000 Fellowship award</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-graduate-fellow-in-environmental-education-and-science-communication-mccall-idaho/4752840992</t>
+  </si>
+  <si>
     <t>Historical Architect Technician (NPS, Southeast Regional Office)</t>
   </si>
   <si>
@@ -655,15 +673,30 @@
     <t>https://greenjobs.greenjobsearch.org/jobs/geographic-information-systems-gis-intern/</t>
   </si>
   <si>
+    <t>Regional Campaign Manager, Southwest</t>
+  </si>
+  <si>
+    <t>Greenlight America</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>Clean Energy</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/regional-campaign-manager-southwest-2/</t>
+  </si>
+  <si>
     <t>Academic Content Manager</t>
   </si>
   <si>
     <t>TalkingPoints</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>Full Time, Temporary</t>
   </si>
   <si>
@@ -694,6 +727,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/d9ac05072b1546ab8791d3ed4b74bc2e-accountant-nyamboyo-technical-school-keroka</t>
   </si>
   <si>
+    <t>Accountant for Non-Profit School</t>
+  </si>
+  <si>
+    <t>KES 20000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d9ac05072b1546ab8791d3ed4b74bc2e-accountant-for-non-profit-school-nyamboyo-technical-school-keroka</t>
+  </si>
+  <si>
     <t>Accounting and Office Manager</t>
   </si>
   <si>
@@ -715,6 +757,42 @@
     <t>https://www.idealist.org/en/job/dfe1b66f48784ca5990ffa9174f4f049-accounting-and-office-manager-the-choice-inc-washington</t>
   </si>
   <si>
+    <t>Accounting Director</t>
+  </si>
+  <si>
+    <t>Christ Church USA</t>
+  </si>
+  <si>
+    <t>Rockaway, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60497c22594c49cfb33970f39e26299f-accounting-director-christ-church-usa-rockaway</t>
+  </si>
+  <si>
+    <t>Administrative Assistant</t>
+  </si>
+  <si>
+    <t>First Congregational Church of Bellingham, WA</t>
+  </si>
+  <si>
+    <t>Bellingham, Washington</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 23.00/hour</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/af1ed3bbce3649c799ccfd1a9f62084a-administrative-assistant-first-congregational-church-of-bellingham-wa-bellingham</t>
+  </si>
+  <si>
     <t>Alumni Associate (SY26-27)</t>
   </si>
   <si>
@@ -730,6 +808,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/f53ef208e4e74e038f4c4f3a6b57e42c-alumni-associate-sy26-27-capital-city-public-charter-school-washington</t>
   </si>
   <si>
+    <t>Arts Education Associate Manager</t>
+  </si>
+  <si>
+    <t>Westhampton Beach Performing Arts Center</t>
+  </si>
+  <si>
+    <t>Westhampton Beach, New York</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c34170e500e8489d88dc343e6d4546a8-arts-education-associate-manager-westhampton-beach-performing-arts-center-westhampton-beach</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General</t>
+  </si>
+  <si>
+    <t>Office of the Massachusetts Attorney General</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 87500.00 - 130595.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/4c62317981534eaa98124fcda4f739ec-assistant-attorney-general-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
     <t>Assistant Litigation Director</t>
   </si>
   <si>
@@ -754,21 +865,33 @@
     <t>Olathe, Kansas</t>
   </si>
   <si>
-    <t>USD 52000.00 - 52000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/47b0e60abec34fa9b28d4197c8cbd73a-associate-community-organizer-direct-action-research-training-center-olathe</t>
   </si>
   <si>
+    <t>Behavioral Youth Counselor - Memphis, TN</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4dd706b87dce43de9dbc4e7256ef8f66-behavioral-youth-counselor-memphis-tn-youth-villages-chicago</t>
+  </si>
+  <si>
     <t>Bilingual SNAP Enrollment Senior Associate (Spanish-Speaking)</t>
   </si>
   <si>
     <t>Project Bread</t>
   </si>
   <si>
-    <t>Boston, Massachusetts</t>
-  </si>
-  <si>
     <t>USD 65000.00 - 67000.00/year</t>
   </si>
   <si>
@@ -778,6 +901,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/a9e013b529944936a56736c0a1075892-bilingual-snap-enrollment-senior-associate-spanish-speaking-project-bread-boston</t>
   </si>
   <si>
+    <t>BLACK RURAL ORGANIZER–IN-TRAINING - Pacific Region &amp; Northwest Region CA, NV, UT, CO, AZ, NM &amp; WA, OR, ID, MT, WY</t>
+  </si>
+  <si>
+    <t>The Chisholm Legacy Project: A Resource Hub for Black Frontline Climate Justice Leadership</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dcd9471219954628a6ef6f70c022a05f-black-rural-organizerin-training-pacific-region-northwest-region-ca-nv-ut-co-az-nm-wa-or-id-mt-wy-the-chisholm-legacy-project-a-resource-hub-for-black-frontline-climate-justice-leadership-denver</t>
+  </si>
+  <si>
+    <t>BLACK RURAL ORGANIZER–IN-TRAINING- Northeast Region- NY, CT, NH, ME, MA, RI, NJ</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/19f417c378e74ce1901517eb9ac3b91b-black-rural-organizerin-training-northeast-region-ny-ct-nh-me-ma-ri-nj-the-chisholm-legacy-project-a-resource-hub-for-black-frontline-climate-justice-leadership-newark</t>
+  </si>
+  <si>
+    <t>Brand Campaign Program Manager</t>
+  </si>
+  <si>
+    <t>Inteleos Inc.</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/75c8ecd8e8384233ac25edd953bd4774-brand-campaign-program-manager-inteleos-inc-rockville</t>
+  </si>
+  <si>
     <t>Business Manager</t>
   </si>
   <si>
@@ -796,6 +955,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/79511bfa729443729e55faf733f4639a-business-manager-morrison-child-and-family-services-portland</t>
   </si>
   <si>
+    <t>Campus Organizer</t>
+  </si>
+  <si>
+    <t>Vote Blue</t>
+  </si>
+  <si>
+    <t>East Lansing, Michigan</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/4ad96ea5fd6a4050bd27002954833f0c-campus-organizer-vote-blue-east-lansing</t>
+  </si>
+  <si>
+    <t>Flagstaff, Arizona</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/00069223711d47328b869b13ffc3ae59-campus-organizer-vote-blue-flagstaff</t>
+  </si>
+  <si>
     <t>Capital City Dedicated Aide (SY26-27)</t>
   </si>
   <si>
@@ -805,6 +988,219 @@
     <t>https://www.idealist.org/en/nonprofit-job/5f903e9921194940aa89600925f2aba5-capital-city-dedicated-aide-sy26-27-capital-city-public-charter-school-washington</t>
   </si>
   <si>
+    <t>Chief Development Officer</t>
+  </si>
+  <si>
+    <t>Cholangiocarcinoma Foundation</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/528a43a842144d1db2b809d467213c2e-chief-development-officer-cholangiocarcinoma-foundation-herriman</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>SEIU Education and Support Fund</t>
+  </si>
+  <si>
+    <t>USD 134444.00 - 165360.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce2cc041b3f949b78f7ff65d5642c962-chief-financial-officer-seiu-education-and-support-fund-northampton</t>
+  </si>
+  <si>
+    <t>Child and Family Therapist - Bilingual English/East African Language</t>
+  </si>
+  <si>
+    <t>Southwest Youth and Family Services</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f931886abc84a17b04ea89a5c05286a-child-and-family-therapist-bilingual-englisheast-african-language-southwest-youth-and-family-services-seattle</t>
+  </si>
+  <si>
+    <t>Child and Family Therapist - Bilingual English/Spanish</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1100b6899814400690264c7b4b4545d1-child-and-family-therapist-bilingual-englishspanish-southwest-youth-and-family-services-seattle</t>
+  </si>
+  <si>
+    <t>Community Organizer</t>
+  </si>
+  <si>
+    <t>Center on Race, Poverty &amp; the Environment</t>
+  </si>
+  <si>
+    <t>Delano, California</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8059ece5c80a40fe8643c02fdf8eda51-community-organizer-center-on-race-poverty-the-environment-delano</t>
+  </si>
+  <si>
+    <t>CRM/ERP and Business Systems Manager</t>
+  </si>
+  <si>
+    <t>Black Women's Health Imperative</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Women, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca1d6fcae67d46dd972a7236c711a60c-crmerp-and-business-systems-manager-black-womens-health-imperative-washington</t>
+  </si>
+  <si>
+    <t>Development &amp; Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>Institute for Nonprofit Practice</t>
+  </si>
+  <si>
+    <t>Dedham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bfe9d2f4f5d24a30b167f72c8b84fa06-development-engagement-coordinator-institute-for-nonprofit-practice-dedham</t>
+  </si>
+  <si>
+    <t>Development &amp; Executive Assistant</t>
+  </si>
+  <si>
+    <t>Culinary Careers Program</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc4064e1a2f84a9f832c65a8c5788b7c-development-executive-assistant-culinary-careers-program-new-york</t>
+  </si>
+  <si>
+    <t>Development Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Showing Up for Racial Justice (SURJ)</t>
+  </si>
+  <si>
+    <t>USD 66500.00 - 66500.00/year</t>
+  </si>
+  <si>
+    <t>Race Ethnicity, Human Rights Civil Liberties, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed7a62a9b01f4368922483e12fe76b01-development-administrative-assistant-showing-up-for-racial-justice-surj-buffalo</t>
+  </si>
+  <si>
+    <t>Director of Compliance</t>
+  </si>
+  <si>
+    <t>Catholic Charities Archdiocese of NY</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc778c5e10b54bc4b49facb97be5db2a-director-of-compliance-catholic-charities-archdiocese-of-ny-bronx-county</t>
+  </si>
+  <si>
+    <t>Director of Housing &amp; Homelessness Prevention</t>
+  </si>
+  <si>
+    <t>Neighborhood Legal Services of Los Angeles County</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 148000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a405dbcfc2e4213a455c3769f0d5c63-director-of-housing-homelessness-prevention-neighborhood-legal-services-of-los-angeles-county-los-angeles</t>
+  </si>
+  <si>
+    <t>Director of Human Resources</t>
+  </si>
+  <si>
+    <t>Glendale, California</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 163000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8dea65845616454bae380de185fda40b-director-of-human-resources-neighborhood-legal-services-of-los-angeles-county-glendale</t>
+  </si>
+  <si>
+    <t>Director of Programs, Marin County</t>
+  </si>
+  <si>
+    <t>Youth Leadership Institute</t>
+  </si>
+  <si>
+    <t>San Rafael, California</t>
+  </si>
+  <si>
+    <t>USD 84694.00 - 96723.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eb2a60957fa8421e9f3b958f0cf2eeb1-director-of-programs-marin-county-youth-leadership-institute-san-rafael</t>
+  </si>
+  <si>
+    <t>Editorial Coordinator</t>
+  </si>
+  <si>
+    <t>Swipe Out Hunger</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa5cad8e954543798f128a6dd502d75c-editorial-coordinator-swipe-out-hunger-los-angeles</t>
+  </si>
+  <si>
     <t>Elementary Associate Teacher (26-27 SY)</t>
   </si>
   <si>
@@ -814,6 +1210,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/56e4f877a68e4cf8911da1331bf0bfcd-elementary-associate-teacher-26-27-sy-capital-city-public-charter-school-washington</t>
   </si>
   <si>
+    <t>ESOL and Digital Literacy Instructor</t>
+  </si>
+  <si>
+    <t>Refugee Artisan Initiative</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 37.00/hour</t>
+  </si>
+  <si>
+    <t>Economic Development, Environment, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f53a76af35a405784e32a42d83e0885-esol-and-digital-literacy-instructor-refugee-artisan-initiative-seattle</t>
+  </si>
+  <si>
     <t>Executive Assistant - King County Library System Foundation</t>
   </si>
   <si>
@@ -823,9 +1237,6 @@
     <t>Issaquah, Washington</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 38.06 - 46.30/hour</t>
   </si>
   <si>
@@ -835,6 +1246,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/b6e3b930b5a2499e8c95e8f272707361-executive-assistant-king-county-library-system-foundation-king-county-library-system-issaquah</t>
   </si>
   <si>
+    <t>Executive Assistant &amp; Board Liaison</t>
+  </si>
+  <si>
+    <t>Miami City Ballet</t>
+  </si>
+  <si>
+    <t>Miami Beach, Florida</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/89a5efec84464753afacd5d969a9f0b7-executive-assistant-board-liaison-miami-city-ballet-miami-beach</t>
+  </si>
+  <si>
+    <t>Executive Assistant to the Chief Patient Officer</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/729f40f3afd2496e8b940d894b92bdfb-executive-assistant-to-the-chief-patient-officer-cholangiocarcinoma-foundation-herriman</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -853,6 +1291,99 @@
     <t>https://www.idealist.org/en/nonprofit-job/3eefc366b9cb43bd807526b0f88aa136-executive-director-redlands-conservancy-redlands</t>
   </si>
   <si>
+    <t>Give a Beat Foundation</t>
+  </si>
+  <si>
+    <t>Los Angeles County, California</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b6f936c9c8aa45cd80a2eddf71d85fb6-executive-director-give-a-beat-foundation-los-angeles-county</t>
+  </si>
+  <si>
+    <t>Globe Northwest</t>
+  </si>
+  <si>
+    <t>Everett, Washington</t>
+  </si>
+  <si>
+    <t>Lgbtq, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f422c5594ccc4d95b9d4db3f8a18220e-executive-director-globe-northwest-everett</t>
+  </si>
+  <si>
+    <t>Executive Director - Cooperating Association</t>
+  </si>
+  <si>
+    <t>Intermountain Natural History Association</t>
+  </si>
+  <si>
+    <t>Vernal, Utah</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e430d02a98914942816fadf40f8e6c88-executive-director-cooperating-association-intermountain-natural-history-association-vernal</t>
+  </si>
+  <si>
+    <t>Executive Director, CAIR-CT</t>
+  </si>
+  <si>
+    <t>Council on American Islamic Relations (Connecticut)</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3cb60f89be41477f8bb22585303a7199-executive-director-cair-ct-council-on-american-islamic-relations-connecticut-new-haven</t>
+  </si>
+  <si>
+    <t>Family Advocate</t>
+  </si>
+  <si>
+    <t>Neighborhood House</t>
+  </si>
+  <si>
+    <t>USD 26.97 - 29.97/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d1bbad33680d4491a91e7b5892fec3f1-family-advocate-neighborhood-house-seattle</t>
+  </si>
+  <si>
+    <t>FAN Program Coordinator</t>
+  </si>
+  <si>
+    <t>Cooper House</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 36.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/2e8279a5a0424952b095591a6deb7f1f-fan-program-coordinator-cooper-house-seattle</t>
+  </si>
+  <si>
     <t>Finance and Operations Manager</t>
   </si>
   <si>
@@ -880,6 +1411,48 @@
     <t>https://www.idealist.org/en/job/7cfa355c420b4426beda7ef61bb0c7ad-finance-manager-economic-studies-job-id-2026-3894-the-brookings-institution-washington</t>
   </si>
   <si>
+    <t>Financial Manager</t>
+  </si>
+  <si>
+    <t>Women's League for Conservative Judaism - WLCJ</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Family, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/48e33e6b3a19433da815834a8c29fb4b-financial-manager-womens-league-for-conservative-judaism-wlcj-new-york</t>
+  </si>
+  <si>
+    <t>Flex Staffing - Program Coordinator - Part-time</t>
+  </si>
+  <si>
+    <t>COMMUNITY SERVICES FOUNDATION</t>
+  </si>
+  <si>
+    <t>WASHINGTON, DC</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/e6d21bfdd9ab4f6d926eece5ad8e0086-flex-staffing-program-coordinator-part-time-community-services-foundation-washington</t>
+  </si>
+  <si>
+    <t>Food Manager</t>
+  </si>
+  <si>
+    <t>Hope House in Crotona Park</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e1ae4873c4ac44648250d6201d693212-food-manager-hope-house-in-crotona-park-bronx-county</t>
+  </si>
+  <si>
     <t>General Counsel</t>
   </si>
   <si>
@@ -892,6 +1465,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/047ac688ef1e44c6ba5cf1d39cc6508f-general-counsel-helen-keller-intl-new-york</t>
   </si>
   <si>
+    <t>General English &amp; Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>Nationalities Service Center</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/656de40125824b0fa18a0d0590c2635b-general-english-volunteer-coordinator-nationalities-service-center-philadelphia</t>
+  </si>
+  <si>
+    <t>Grant Lifecycle Management &amp; Data Analyst</t>
+  </si>
+  <si>
+    <t>NAMI Illinois</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/087488e09fbf4290bfb9778830ce4f9f-grant-lifecycle-management-data-analyst-nami-illinois-chicago</t>
+  </si>
+  <si>
+    <t>Grant Writer</t>
+  </si>
+  <si>
+    <t>USD 71000.00 - 89000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/82b3e6bcda3940e292971fc9ca463a17-grant-writer-neighborhood-legal-services-of-los-angeles-county-glendale</t>
+  </si>
+  <si>
     <t>Grants &amp; Program Compliance Coordinator</t>
   </si>
   <si>
@@ -916,9 +1531,6 @@
     <t>NYC Campaign Finance Board</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 70000.00 - 80000.00/year</t>
   </si>
   <si>
@@ -976,6 +1588,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/f4cf5b2404f0454681fe7051feaa7918-high-school-world-language-teacher-sy-26-27-capital-city-public-charter-school-washington</t>
   </si>
   <si>
+    <t>IT/Cybersecurity RFP</t>
+  </si>
+  <si>
+    <t>Nest Inc.</t>
+  </si>
+  <si>
+    <t>USD 20000.00 - 25000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Economic Development, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5ac638f2220c4f35b58ac0ff1932c725-itcybersecurity-rfp-nest-inc-new-york</t>
+  </si>
+  <si>
+    <t>Language Strategy Manager</t>
+  </si>
+  <si>
+    <t>USD 105001.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f7d1b273ecc7478b93787b3bcab6d9bf-language-strategy-manager-nyc-campaign-finance-board-new-york</t>
+  </si>
+  <si>
     <t>LEA Daily Substitute Teacher (SY 26-27)</t>
   </si>
   <si>
@@ -985,6 +1624,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/006a24a9dcd0421b9368ffa8b7a9880a-lea-daily-substitute-teacher-sy-26-27-capital-city-public-charter-school-washington</t>
   </si>
   <si>
+    <t>Let's Go Coordinator</t>
+  </si>
+  <si>
+    <t>Cascade Bicycle Club</t>
+  </si>
+  <si>
+    <t>USD 28.13 - 39.38/hour</t>
+  </si>
+  <si>
+    <t>Education, Transportation, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e612db977be45f3857c69bcb5cb1d33-lets-go-coordinator-cascade-bicycle-club-seattle</t>
+  </si>
+  <si>
+    <t>Litigation Associate Supervising Attorney</t>
+  </si>
+  <si>
+    <t>USD 103000.00 - 117000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bcbae6916cdd43f0ac03a6f93af97670-litigation-associate-supervising-attorney-neighborhood-legal-services-of-los-angeles-county-los-angeles</t>
+  </si>
+  <si>
     <t>Major Donor Associate</t>
   </si>
   <si>
@@ -1033,6 +1699,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/c50895c27ef74462ae2fc2219298eabd-major-gifts-officer-riverkeeper-ossining</t>
   </si>
   <si>
+    <t>Manager of Individual Giving</t>
+  </si>
+  <si>
+    <t>The Unusual Suspects Theatre Company</t>
+  </si>
+  <si>
+    <t>Pasadena, California</t>
+  </si>
+  <si>
+    <t>USD 75750.00 - 78750.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6fcdb31210144f80a2eb86c58ea31c0a-manager-of-individual-giving-the-unusual-suspects-theatre-company-pasadena</t>
+  </si>
+  <si>
     <t>Manager, Neighborhoods</t>
   </si>
   <si>
@@ -1045,6 +1729,27 @@
     <t>https://www.idealist.org/en/job/85893e8841ff4dee8ee1931a6f708078-manager-neighborhoods-nyc-campaign-finance-board-new-york</t>
   </si>
   <si>
+    <t>Office Administrator/Receptionist</t>
+  </si>
+  <si>
+    <t>Nazareth Housing</t>
+  </si>
+  <si>
+    <t>USD 42000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b1faa2179b2a4ea490954abccdce84d7-office-administratorreceptionist-nazareth-housing-bronx-county</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/dfe1b66f48784ca5990ffa9174f4f049-operations-manager-the-choice-inc-washington</t>
+  </si>
+  <si>
     <t>Outreach Coordinator</t>
   </si>
   <si>
@@ -1057,6 +1762,66 @@
     <t>https://www.idealist.org/en/job/379f54d9aebe44b4b089b97f3db92d0d-outreach-coordinator-nyc-campaign-finance-board-new-york</t>
   </si>
   <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>Mobilization for Justice</t>
+  </si>
+  <si>
+    <t>USD 63654.00 - 110049.33/year</t>
+  </si>
+  <si>
+    <t>Family, Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d7935e9de48c4356b06c5169073c7007-paralegal-mobilization-for-justice-new-york</t>
+  </si>
+  <si>
+    <t>Paralegal – Consumer Debt &amp; Bankruptcy</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ffc21280414d4b988e150d078e1492c6-paralegal-consumer-debt-bankruptcy-neighborhood-legal-services-of-los-angeles-county-los-angeles</t>
+  </si>
+  <si>
+    <t>Part Time Marketing and Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>WAQRR - Washington Alliance for Quality Recovery Residences</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e1f2c50e029645f4a7294373df5f14b8-part-time-marketing-and-engagement-coordinator-waqrr-washington-alliance-for-quality-recovery-residences-mount-vernon</t>
+  </si>
+  <si>
+    <t>Part-Time Campaign Organizer</t>
+  </si>
+  <si>
+    <t>The Outreach Team</t>
+  </si>
+  <si>
+    <t>Grand Island, Nebraska</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/73588ebb25c246eca19879c510ba2046-part-time-campaign-organizer-the-outreach-team-grand-island</t>
+  </si>
+  <si>
     <t>Philanthropy &amp; Grants Manager</t>
   </si>
   <si>
@@ -1075,6 +1840,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/e8c444a057954822a73b187ef54071ae-philanthropy-grants-manager-olympic-housing-trust-port-townsend</t>
   </si>
   <si>
+    <t>Philanthropy and Grants Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e8c444a057954822a73b187ef54071ae-philanthropy-and-grants-manager-olympic-housing-trust-port-townsend</t>
+  </si>
+  <si>
     <t>Placement Officer, College Scholars Program</t>
   </si>
   <si>
@@ -1084,24 +1855,33 @@
     <t>Newark, NJ</t>
   </si>
   <si>
-    <t>USD 55000.00 - 55000.00/year</t>
-  </si>
-  <si>
     <t>Children Youth, Education</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/d6637e21cb224739990bd0a69a346f47-placement-officer-college-scholars-program-seeds-access-changes-everything-newark</t>
   </si>
   <si>
+    <t>Policy Fellow</t>
+  </si>
+  <si>
+    <t>LA County Office of Food Systems</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Hunger Food Security, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1011003ac4be43b398787ffa2f89589a-policy-fellow-la-county-office-of-food-systems-los-angeles</t>
+  </si>
+  <si>
     <t>President &amp; Chief Executive Officer</t>
   </si>
   <si>
     <t>Friends of Waterfront Park</t>
   </si>
   <si>
-    <t>Seattle, Washington</t>
-  </si>
-  <si>
     <t>USD 280000.00 - 340000.00/year</t>
   </si>
   <si>
@@ -1111,12 +1891,135 @@
     <t>https://www.idealist.org/en/nonprofit-job/4b9ad9492f2146d3b250e30a15f1a071-president-chief-executive-officer-friends-of-waterfront-park-seattle</t>
   </si>
   <si>
+    <t>Pro Bono Staff Attorney</t>
+  </si>
+  <si>
+    <t>Family Legal Care</t>
+  </si>
+  <si>
+    <t>Remote (New York, New York)</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 77000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f14b2a934b05471bb4732d4f19538f84-pro-bono-staff-attorney-family-legal-care-new-york</t>
+  </si>
+  <si>
+    <t>Program Assistant - Senior Center</t>
+  </si>
+  <si>
+    <t>Golden Gate Senior Services</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Disability, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3d3d6acadc8e44669bf86e9aa481b9c0-program-assistant-senior-center-golden-gate-senior-services-san-francisco</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>Planted Society</t>
+  </si>
+  <si>
+    <t>Animals, Civic Engagement, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eaf2666830ae4fe4b7be3a06434a5916-program-manager-planted-society-austin</t>
+  </si>
+  <si>
+    <t>Program Officer, Science</t>
+  </si>
+  <si>
+    <t>The Peter and Carmen Lucia Buck Foundation</t>
+  </si>
+  <si>
+    <t>USD 46000.00 - 53000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7e0d7651d17e416783d0a4c28f5d4470-program-officer-science-the-peter-and-carmen-lucia-buck-foundation-new-york</t>
+  </si>
+  <si>
     <t>Programs Officer, College Scholars Program</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/d420a116b695410ebeabdebf5c309699-programs-officer-college-scholars-program-seeds-access-changes-everything-newark</t>
   </si>
   <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>Immigrant Legal Resource Center</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 108000.00 - 116000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d01e888b6eca4ce0be25c7664d05b002-project-manager-immigrant-legal-resource-center-fresno</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9c74995ddc5c4a6e8d78a1a0fee4524b-project-manager-immigrant-legal-resource-center-san-francisco</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/14c0bc985b8741ddaa5b675d55b45007-project-manager-immigrant-legal-resource-center-los-angeles</t>
+  </si>
+  <si>
+    <t>Proofreader – Temporary, Remote</t>
+  </si>
+  <si>
+    <t>Sanky Communications, Inc.</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/97f59782cb4b4a4d8793c0ac6591b80b-proofreader-temporary-remote-sanky-communications-inc-new-york</t>
+  </si>
+  <si>
+    <t>Quality Improvement Associate- Office of Mental Health</t>
+  </si>
+  <si>
+    <t>Services for the UnderServed</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Job Workplace, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6399b607d74b4058b431e217a509e03b-quality-improvement-associate-office-of-mental-health-services-for-the-underserved-new-york</t>
+  </si>
+  <si>
+    <t>Registered Nurse</t>
+  </si>
+  <si>
+    <t>Job Path, Inc.</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d0f2604d9ed64b35a3f36bb23a3a1dc8-registered-nurse-job-path-inc-new-york</t>
+  </si>
+  <si>
     <t>Request for Proposals (RFP) - CRM Platform Selection</t>
   </si>
   <si>
@@ -1132,6 +2035,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/21f587f60b9048be8585a82560baa4ca-request-for-proposals-rfp-crm-platform-selection-nonviolence-international-washington</t>
   </si>
   <si>
+    <t>Research assistant on nonprofit burnout prevention</t>
+  </si>
+  <si>
+    <t>Fund the People</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Philanthropy, Job Workplace, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/579c1e9e7b174681b360a5c09cede93a-research-assistant-on-nonprofit-burnout-prevention-fund-the-people-beacon</t>
+  </si>
+  <si>
+    <t>Resource Navigator</t>
+  </si>
+  <si>
+    <t>Tukwila, Washington</t>
+  </si>
+  <si>
+    <t>USD 29.59 - 32.82/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/059fc9eda8924229b6026afad741cf64-resource-navigator-neighborhood-house-tukwila</t>
+  </si>
+  <si>
+    <t>Resource Navigator- Bilingual in Farsi and Dari</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc9eec6640bc4d49b5d5fddca9db5ed5-resource-navigator-bilingual-in-farsi-and-dari-neighborhood-house-tukwila</t>
+  </si>
+  <si>
     <t>Resources Specialist</t>
   </si>
   <si>
@@ -1189,6 +2125,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/5bbcab4486814e2bb8a8daa992210f56-senior-administrative-assistant-center-for-holocaust-human-rights-genocide-education-at-brookdale-community-college-lincroft</t>
   </si>
   <si>
+    <t>SENIOR ASSET MANAGER</t>
+  </si>
+  <si>
+    <t>NeighborWorks Affiliates</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e8614f39954b448ebac2cb3b929d4e75-senior-asset-manager-neighborworks-affiliates-boston</t>
+  </si>
+  <si>
     <t>Senior Associate for Library Production</t>
   </si>
   <si>
@@ -1204,6 +2155,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/37ecab4b7257423eac7e12bbb153cf38-senior-associate-for-library-production-freedom-reads-hamden</t>
   </si>
   <si>
+    <t>Senior Consultant, Workforce Development &amp; Training</t>
+  </si>
+  <si>
+    <t>BME Strategies</t>
+  </si>
+  <si>
+    <t>Remote (Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 91520.00 - 151840.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/deb795968c8c4256beff22d1db035f23-senior-consultant-workforce-development-training-bme-strategies-north-andover</t>
+  </si>
+  <si>
     <t>Senior Digital Fundraising Manager</t>
   </si>
   <si>
@@ -1237,6 +2203,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/5bb9a30a97ba47a19c17cf75db54c635-senior-digital-fundraising-specialist-gbh-boston</t>
   </si>
   <si>
+    <t>Senior Director, Grants &amp; Contracts</t>
+  </si>
+  <si>
+    <t>AIDS Foundation of Chicago</t>
+  </si>
+  <si>
+    <t>USD 102984.06 - 121104.75/year</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ccfc1998aa2e46b4a286fd27247b31ad-senior-director-grants-contracts-aids-foundation-of-chicago-chicago</t>
+  </si>
+  <si>
     <t>Senior Director, National Campaign</t>
   </si>
   <si>
@@ -1252,6 +2233,78 @@
     <t>https://www.idealist.org/en/nonprofit-job/5c2957f031374d4a80603350ad815360-senior-director-national-campaign-human-rights-campaign-washington</t>
   </si>
   <si>
+    <t>Senior Financial Analyst</t>
+  </si>
+  <si>
+    <t>Vision To Learn</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/98b7c665d48145c9ad2cc102647c14ce-senior-financial-analyst-vision-to-learn-los-angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5fa52dc824c744a3b5b969ad50661f57-senior-financial-analyst-vision-to-learn-los-angeles</t>
+  </si>
+  <si>
+    <t>Senior Manager, Individual Philanthropy</t>
+  </si>
+  <si>
+    <t>Animal Care Centers of NYC</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8327af0d1f4d438e8f1f85c7c2fe5c1d-senior-manager-individual-philanthropy-animal-care-centers-of-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Senior Manager, State Policy &amp; Advocacy</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26c6a31fe8834cac982cc1dd01c1640b-senior-manager-state-policy-advocacy-aids-foundation-of-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Senior Manager, Talent Development</t>
+  </si>
+  <si>
+    <t>Environmental Defense Fund</t>
+  </si>
+  <si>
+    <t>USD 125500.00 - 133000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bcb6aea5428a43d3bb60f7a8a4ef5cb4-senior-manager-talent-development-environmental-defense-fund-new-york</t>
+  </si>
+  <si>
+    <t>Senior Program Manager</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3378330040714ab3b83ddc733bcdd836-senior-program-manager-refugee-artisan-initiative-seattle</t>
+  </si>
+  <si>
+    <t>Senior Specialist, Talent Development</t>
+  </si>
+  <si>
+    <t>USD 83500.00 - 88500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a64f32853e8b44a09a3a3ee842d64be9-senior-specialist-talent-development-environmental-defense-fund-new-york</t>
+  </si>
+  <si>
     <t>Senior Staff Attorney, Child Welfare Litigation</t>
   </si>
   <si>
@@ -1267,6 +2320,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/5314f3ccc3de44449e10545b1d058079-senior-staff-attorney-child-welfare-litigation-a-better-childhood-new-york</t>
   </si>
   <si>
+    <t>Service Enriched Housing Super Hero</t>
+  </si>
+  <si>
+    <t>Community Housing Resource Partners, Inc.</t>
+  </si>
+  <si>
+    <t>Creedmoor, Texas</t>
+  </si>
+  <si>
+    <t>USD 16.00 - 16.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d086acd8fc9c43fb954e7d10be3695ae-service-enriched-housing-super-hero-community-housing-resource-partners-inc-creedmoor</t>
+  </si>
+  <si>
+    <t>Shelter Youth Advocate</t>
+  </si>
+  <si>
+    <t>Bradley Angle</t>
+  </si>
+  <si>
+    <t>USD 29.50/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6084b9a216f54127801d8b73dad3b888-shelter-youth-advocate-bradley-angle-portland</t>
+  </si>
+  <si>
     <t>Site Coordinator - Reading High School, Reading School District</t>
   </si>
   <si>
@@ -1279,9 +2362,6 @@
     <t>USD 45000.00 - 50000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Education, Family</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/b042c860d00846ad910e611557955f8f-site-coordinator-reading-high-school-reading-school-district-communities-in-schools-of-eastern-pa-reading</t>
   </si>
   <si>
@@ -1327,9 +2407,6 @@
     <t>Legal Clinic for the Disabled</t>
   </si>
   <si>
-    <t>Philadelphia, Pennsylvania</t>
-  </si>
-  <si>
     <t>USD 67500.00/year</t>
   </si>
   <si>
@@ -1339,6 +2416,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/8a07af2a17474d4fa929151963902553-staff-attorney-housing-habitability-legal-clinic-for-the-disabled-philadelphia</t>
   </si>
   <si>
+    <t>Staff Attorney - Lawyers Preventing and Ending Homelessness Project (PEHP)</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4efa678e7c454fc89ace3ff0015ddd69-staff-attorney-lawyers-preventing-and-ending-homelessness-project-pehp-neighborhood-legal-services-of-los-angeles-county-los-angeles</t>
+  </si>
+  <si>
+    <t>Staff Attorney – Stay Housed LA Program</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a174024507d42aeabd02ba5480507bd-staff-attorney-stay-housed-la-program-neighborhood-legal-services-of-los-angeles-county-glendale</t>
+  </si>
+  <si>
+    <t>Staff Attorney- Family Law</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02478ab0b55e41fab1b4a7e847868886-staff-attorney-family-law-neighborhood-legal-services-of-los-angeles-county-los-angeles</t>
+  </si>
+  <si>
+    <t>Staff Attorney- Pomona Self-Help</t>
+  </si>
+  <si>
+    <t>Pomona, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fc86566c78a84c55aecb87c7c99c6153-staff-attorney-pomona-self-help-neighborhood-legal-services-of-los-angeles-county-pomona</t>
+  </si>
+  <si>
     <t>Staff Attorney, Child Welfare Litigation</t>
   </si>
   <si>
@@ -1360,6 +2467,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/11d5658b784e40efb90862791c6071d7-student-advisor-gwhs-east-side-house-settlement-new-york</t>
   </si>
   <si>
+    <t>Supportive Care Specialist (1:1)</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Disability, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/940602a6187849aba0dda90d1f4f749f-supportive-care-specialist-11-golden-gate-senior-services-san-francisco</t>
+  </si>
+  <si>
+    <t>Temporary Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 83811.10 - 93567.35/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0f5605098c7e4d2fa62347a6e3556b71-temporary-staff-attorney-mobilization-for-justice-new-york</t>
+  </si>
+  <si>
+    <t>Temporary Staff Attorney - Immigration Law Project</t>
+  </si>
+  <si>
+    <t>USD 93567.35 - 141629.79/year</t>
+  </si>
+  <si>
+    <t>Family, Job Workplace, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/84441733b851412ca73f93a16d010ece-temporary-staff-attorney-immigration-law-project-mobilization-for-justice-new-york</t>
+  </si>
+  <si>
+    <t>The Dream Program--Executive Director</t>
+  </si>
+  <si>
+    <t>The Dream Program</t>
+  </si>
+  <si>
+    <t>Ocean Springs, Mississippi</t>
+  </si>
+  <si>
+    <t>Arts Music, Disability, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/135c9f9b645742d3883e32181453478f-the-dream-program-executive-director-the-dream-program-ocean-springs</t>
+  </si>
+  <si>
     <t>Training &amp; Clinical Coaching Coordinator - Clinical Supports Program</t>
   </si>
   <si>
@@ -1372,6 +2527,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/29c4025145814412be263e52affb60c0-training-clinical-coaching-coordinator-clinical-supports-program-safe-horizon-new-york</t>
   </si>
   <si>
+    <t>Training Director</t>
+  </si>
+  <si>
+    <t>Impact Fund</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 147149.00/year</t>
+  </si>
+  <si>
+    <t>Education, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3588a567220f48b0b878578d83131677-training-director-impact-fund-berkeley</t>
+  </si>
+  <si>
     <t>Utah Organizer</t>
   </si>
   <si>
@@ -1393,9 +2566,6 @@
     <t>Volunteer Coordinator</t>
   </si>
   <si>
-    <t>Civic Engagement</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/job/d129fc64398945a7ac65043c914dd8e6-volunteer-coordinator-nyc-campaign-finance-board-new-york</t>
   </si>
   <si>
@@ -1532,9 +2702,6 @@
   </si>
   <si>
     <t>Sustainable Connections</t>
-  </si>
-  <si>
-    <t>Bellingham, Washington</t>
   </si>
   <si>
     <t>Fund Development</t>
@@ -2100,7 +3267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2656,36 +3823,36 @@
         <v>134</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="E24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F25" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>142</v>
@@ -2719,42 +3886,42 @@
         <v>149</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
       </c>
       <c r="E27" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>153</v>
+        <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E28" t="s">
-        <v>154</v>
+        <v>43</v>
       </c>
       <c r="F28" t="s">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>156</v>
@@ -2771,7 +3938,7 @@
         <v>159</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
         <v>160</v>
@@ -2788,36 +3955,36 @@
         <v>163</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="C30" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F30" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s">
         <v>170</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E31" t="s">
         <v>171</v>
@@ -2834,183 +4001,206 @@
         <v>174</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>175</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>176</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F32" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
       </c>
       <c r="E33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="C34" t="s">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
       </c>
       <c r="E34" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F34" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s">
         <v>107</v>
       </c>
       <c r="C35" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
       </c>
       <c r="E35" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F35" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
       </c>
       <c r="E36" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F36" t="s">
-        <v>49</v>
+        <v>172</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B37" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="C37" t="s">
-        <v>192</v>
+        <v>66</v>
       </c>
       <c r="D37" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E37" t="s">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="F37" t="s">
-        <v>193</v>
+        <v>49</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B38" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C38" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="F38" t="s">
-        <v>125</v>
+        <v>199</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B39" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C39" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
       </c>
       <c r="E39" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F39" t="s">
-        <v>204</v>
+        <v>125</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>205</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>206</v>
+      </c>
+      <c r="B40" t="s">
+        <v>207</v>
+      </c>
+      <c r="C40" t="s">
+        <v>208</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" t="s">
+        <v>209</v>
+      </c>
+      <c r="F40" t="s">
+        <v>210</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -3054,6 +4244,7 @@
     <hyperlink ref="H37" r:id="rId36"/>
     <hyperlink ref="H38" r:id="rId37"/>
     <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3062,7 +4253,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3103,31 +4294,55 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3136,7 +4351,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3177,1221 +4392,3222 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D2" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="E2" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="F2" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C3" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D3" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="E3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F3" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D4" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E4" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F4" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B5" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C5" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="D5" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="F5" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="B6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="C6" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="D6" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="F6" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B7" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C7" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D7" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="E7" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="F7" t="s">
-        <v>210</v>
+        <v>257</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="B8" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="C8" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D8" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="F8" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="B9" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C9" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D9" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="F9" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="B10" t="s">
-        <v>234</v>
+        <v>271</v>
       </c>
       <c r="C10" t="s">
-        <v>228</v>
+        <v>272</v>
       </c>
       <c r="D10" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="F10" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B11" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="C11" t="s">
-        <v>228</v>
+        <v>277</v>
       </c>
       <c r="D11" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="F11" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D12" t="s">
+        <v>243</v>
+      </c>
+      <c r="E12" t="s">
         <v>267</v>
       </c>
-      <c r="C12" t="s">
-        <v>268</v>
-      </c>
-      <c r="D12" t="s">
-        <v>269</v>
-      </c>
-      <c r="E12" t="s">
-        <v>270</v>
-      </c>
       <c r="F12" t="s">
-        <v>271</v>
+        <v>216</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="B13" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C13" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="D13" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="F13" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="B14" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="C14" t="s">
-        <v>215</v>
+        <v>272</v>
       </c>
       <c r="D14" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="F14" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="B15" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="C15" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D15" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F15" t="s">
-        <v>210</v>
+        <v>298</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B16" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="C16" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D16" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="F16" t="s">
-        <v>210</v>
+        <v>298</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B17" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="C17" t="s">
-        <v>294</v>
+        <v>221</v>
       </c>
       <c r="D17" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="F17" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B18" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C18" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="D18" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="F18" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="B19" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="C19" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D19" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="E19" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="F19" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B20" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C20" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="D20" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E20" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F20" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B21" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="C21" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="D21" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F21" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B22" t="s">
-        <v>234</v>
+        <v>325</v>
       </c>
       <c r="C22" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D22" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="F22" t="s">
-        <v>236</v>
+        <v>305</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B23" t="s">
-        <v>234</v>
+        <v>329</v>
       </c>
       <c r="C23" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D23" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F23" t="s">
-        <v>236</v>
+        <v>331</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B24" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C24" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="D24" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>326</v>
+        <v>244</v>
       </c>
       <c r="F24" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B25" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C25" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="D25" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="F25" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B26" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C26" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="D26" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="F26" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B27" t="s">
-        <v>299</v>
+        <v>347</v>
       </c>
       <c r="C27" t="s">
-        <v>300</v>
+        <v>221</v>
       </c>
       <c r="D27" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F27" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B28" t="s">
-        <v>299</v>
+        <v>352</v>
       </c>
       <c r="C28" t="s">
-        <v>300</v>
+        <v>353</v>
       </c>
       <c r="D28" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="F28" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="B29" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="C29" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="D29" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="F29" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="B30" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="C30" t="s">
-        <v>355</v>
+        <v>221</v>
       </c>
       <c r="D30" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="F30" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B31" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="C31" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="D31" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F31" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="B32" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="C32" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="D32" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>246</v>
+        <v>377</v>
       </c>
       <c r="F32" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="B33" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="C33" t="s">
-        <v>215</v>
+        <v>381</v>
       </c>
       <c r="D33" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="F33" t="s">
-        <v>370</v>
+        <v>216</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B34" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C34" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D34" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="F34" t="s">
-        <v>258</v>
+        <v>388</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="B35" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="C35" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D35" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="F35" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="B36" t="s">
-        <v>373</v>
+        <v>260</v>
       </c>
       <c r="C36" t="s">
-        <v>374</v>
+        <v>242</v>
       </c>
       <c r="D36" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="F36" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="B37" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="C37" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="D37" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E37" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="F37" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="B38" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="C38" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="D38" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="E38" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="F38" t="s">
-        <v>210</v>
+        <v>408</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="B39" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="C39" t="s">
-        <v>215</v>
+        <v>412</v>
       </c>
       <c r="D39" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="F39" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="B40" t="s">
-        <v>402</v>
+        <v>325</v>
       </c>
       <c r="C40" t="s">
-        <v>403</v>
+        <v>221</v>
       </c>
       <c r="D40" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="F40" t="s">
-        <v>405</v>
+        <v>305</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="B41" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C41" t="s">
-        <v>66</v>
+        <v>421</v>
       </c>
       <c r="D41" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="F41" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B42" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="C42" t="s">
-        <v>300</v>
+        <v>426</v>
       </c>
       <c r="D42" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="F42" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="C43" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="D43" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="E43" t="s">
-        <v>420</v>
+        <v>228</v>
       </c>
       <c r="F43" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="B44" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="C44" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="D44" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="F44" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="B45" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="C45" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="D45" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="F45" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="B46" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="C46" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
       <c r="D46" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="F46" t="s">
-        <v>433</v>
+        <v>336</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="B47" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="C47" t="s">
-        <v>437</v>
+        <v>400</v>
       </c>
       <c r="D47" t="s">
-        <v>229</v>
+        <v>452</v>
       </c>
       <c r="E47" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="F47" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="B48" t="s">
-        <v>413</v>
+        <v>457</v>
       </c>
       <c r="C48" t="s">
-        <v>300</v>
+        <v>221</v>
       </c>
       <c r="D48" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="E48" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="F48" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="B49" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="C49" t="s">
-        <v>300</v>
+        <v>242</v>
       </c>
       <c r="D49" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>295</v>
+        <v>463</v>
       </c>
       <c r="F49" t="s">
-        <v>446</v>
+        <v>216</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="B50" t="s">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="C50" t="s">
-        <v>300</v>
+        <v>359</v>
       </c>
       <c r="D50" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="F50" t="s">
-        <v>210</v>
+        <v>468</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="B51" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="C51" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="D51" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="F51" t="s">
-        <v>456</v>
+        <v>216</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="B52" t="s">
-        <v>299</v>
+        <v>476</v>
       </c>
       <c r="C52" t="s">
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="D52" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>344</v>
+        <v>297</v>
       </c>
       <c r="F52" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="B53" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="C53" t="s">
-        <v>463</v>
+        <v>221</v>
       </c>
       <c r="D53" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>420</v>
+        <v>481</v>
       </c>
       <c r="F53" t="s">
-        <v>464</v>
+        <v>216</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="B54" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="C54" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="D54" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="F54" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>471</v>
+        <v>488</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>489</v>
+      </c>
+      <c r="B55" t="s">
+        <v>490</v>
+      </c>
+      <c r="C55" t="s">
+        <v>286</v>
+      </c>
+      <c r="D55" t="s">
+        <v>243</v>
+      </c>
+      <c r="E55" t="s">
+        <v>491</v>
+      </c>
+      <c r="F55" t="s">
+        <v>492</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>494</v>
+      </c>
+      <c r="B56" t="s">
+        <v>375</v>
+      </c>
+      <c r="C56" t="s">
+        <v>381</v>
+      </c>
+      <c r="D56" t="s">
+        <v>243</v>
+      </c>
+      <c r="E56" t="s">
+        <v>495</v>
+      </c>
+      <c r="F56" t="s">
+        <v>378</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>497</v>
+      </c>
+      <c r="B57" t="s">
+        <v>498</v>
+      </c>
+      <c r="C57" t="s">
+        <v>499</v>
+      </c>
+      <c r="D57" t="s">
+        <v>243</v>
+      </c>
+      <c r="E57" t="s">
+        <v>500</v>
+      </c>
+      <c r="F57" t="s">
+        <v>501</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>503</v>
+      </c>
+      <c r="B58" t="s">
+        <v>504</v>
+      </c>
+      <c r="C58" t="s">
+        <v>359</v>
+      </c>
+      <c r="D58" t="s">
+        <v>243</v>
+      </c>
+      <c r="E58" t="s">
+        <v>505</v>
+      </c>
+      <c r="F58" t="s">
+        <v>506</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>508</v>
+      </c>
+      <c r="B59" t="s">
+        <v>509</v>
+      </c>
+      <c r="C59" t="s">
+        <v>510</v>
+      </c>
+      <c r="D59" t="s">
+        <v>227</v>
+      </c>
+      <c r="E59" t="s">
+        <v>511</v>
+      </c>
+      <c r="F59" t="s">
+        <v>512</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>514</v>
+      </c>
+      <c r="B60" t="s">
+        <v>515</v>
+      </c>
+      <c r="C60" t="s">
+        <v>359</v>
+      </c>
+      <c r="D60" t="s">
+        <v>243</v>
+      </c>
+      <c r="E60" t="s">
+        <v>516</v>
+      </c>
+      <c r="F60" t="s">
+        <v>517</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>519</v>
+      </c>
+      <c r="B61" t="s">
+        <v>260</v>
+      </c>
+      <c r="C61" t="s">
+        <v>242</v>
+      </c>
+      <c r="D61" t="s">
+        <v>243</v>
+      </c>
+      <c r="E61" t="s">
+        <v>520</v>
+      </c>
+      <c r="F61" t="s">
+        <v>262</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>522</v>
+      </c>
+      <c r="B62" t="s">
+        <v>260</v>
+      </c>
+      <c r="C62" t="s">
+        <v>242</v>
+      </c>
+      <c r="D62" t="s">
+        <v>243</v>
+      </c>
+      <c r="E62" t="s">
+        <v>520</v>
+      </c>
+      <c r="F62" t="s">
+        <v>262</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>524</v>
+      </c>
+      <c r="B63" t="s">
+        <v>525</v>
+      </c>
+      <c r="C63" t="s">
+        <v>221</v>
+      </c>
+      <c r="D63" t="s">
+        <v>234</v>
+      </c>
+      <c r="E63" t="s">
+        <v>526</v>
+      </c>
+      <c r="F63" t="s">
+        <v>527</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>529</v>
+      </c>
+      <c r="B64" t="s">
+        <v>504</v>
+      </c>
+      <c r="C64" t="s">
+        <v>359</v>
+      </c>
+      <c r="D64" t="s">
+        <v>243</v>
+      </c>
+      <c r="E64" t="s">
+        <v>530</v>
+      </c>
+      <c r="F64" t="s">
+        <v>531</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>533</v>
+      </c>
+      <c r="B65" t="s">
+        <v>260</v>
+      </c>
+      <c r="C65" t="s">
+        <v>242</v>
+      </c>
+      <c r="D65" t="s">
+        <v>234</v>
+      </c>
+      <c r="E65" t="s">
+        <v>534</v>
+      </c>
+      <c r="F65" t="s">
+        <v>262</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>536</v>
+      </c>
+      <c r="B66" t="s">
+        <v>537</v>
+      </c>
+      <c r="C66" t="s">
+        <v>335</v>
+      </c>
+      <c r="D66" t="s">
+        <v>243</v>
+      </c>
+      <c r="E66" t="s">
+        <v>538</v>
+      </c>
+      <c r="F66" t="s">
+        <v>539</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>541</v>
+      </c>
+      <c r="B67" t="s">
+        <v>375</v>
+      </c>
+      <c r="C67" t="s">
+        <v>376</v>
+      </c>
+      <c r="D67" t="s">
+        <v>243</v>
+      </c>
+      <c r="E67" t="s">
+        <v>542</v>
+      </c>
+      <c r="F67" t="s">
+        <v>543</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>545</v>
+      </c>
+      <c r="B68" t="s">
+        <v>546</v>
+      </c>
+      <c r="C68" t="s">
+        <v>547</v>
+      </c>
+      <c r="D68" t="s">
+        <v>243</v>
+      </c>
+      <c r="E68" t="s">
+        <v>548</v>
+      </c>
+      <c r="F68" t="s">
+        <v>549</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>551</v>
+      </c>
+      <c r="B69" t="s">
+        <v>546</v>
+      </c>
+      <c r="C69" t="s">
+        <v>547</v>
+      </c>
+      <c r="D69" t="s">
+        <v>243</v>
+      </c>
+      <c r="E69" t="s">
+        <v>552</v>
+      </c>
+      <c r="F69" t="s">
+        <v>553</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>555</v>
+      </c>
+      <c r="B70" t="s">
+        <v>556</v>
+      </c>
+      <c r="C70" t="s">
+        <v>557</v>
+      </c>
+      <c r="D70" t="s">
+        <v>243</v>
+      </c>
+      <c r="E70" t="s">
+        <v>558</v>
+      </c>
+      <c r="F70" t="s">
+        <v>559</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>561</v>
+      </c>
+      <c r="B71" t="s">
+        <v>562</v>
+      </c>
+      <c r="C71" t="s">
+        <v>563</v>
+      </c>
+      <c r="D71" t="s">
+        <v>243</v>
+      </c>
+      <c r="E71" t="s">
+        <v>564</v>
+      </c>
+      <c r="F71" t="s">
+        <v>565</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>567</v>
+      </c>
+      <c r="B72" t="s">
+        <v>504</v>
+      </c>
+      <c r="C72" t="s">
+        <v>359</v>
+      </c>
+      <c r="D72" t="s">
+        <v>243</v>
+      </c>
+      <c r="E72" t="s">
+        <v>568</v>
+      </c>
+      <c r="F72" t="s">
+        <v>569</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>571</v>
+      </c>
+      <c r="B73" t="s">
+        <v>572</v>
+      </c>
+      <c r="C73" t="s">
+        <v>370</v>
+      </c>
+      <c r="D73" t="s">
+        <v>243</v>
+      </c>
+      <c r="E73" t="s">
+        <v>573</v>
+      </c>
+      <c r="F73" t="s">
+        <v>574</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>576</v>
+      </c>
+      <c r="B74" t="s">
+        <v>241</v>
+      </c>
+      <c r="C74" t="s">
+        <v>242</v>
+      </c>
+      <c r="D74" t="s">
+        <v>243</v>
+      </c>
+      <c r="E74" t="s">
+        <v>244</v>
+      </c>
+      <c r="F74" t="s">
+        <v>245</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>578</v>
+      </c>
+      <c r="B75" t="s">
+        <v>504</v>
+      </c>
+      <c r="C75" t="s">
+        <v>359</v>
+      </c>
+      <c r="D75" t="s">
+        <v>243</v>
+      </c>
+      <c r="E75" t="s">
+        <v>579</v>
+      </c>
+      <c r="F75" t="s">
+        <v>580</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>582</v>
+      </c>
+      <c r="B76" t="s">
+        <v>583</v>
+      </c>
+      <c r="C76" t="s">
+        <v>359</v>
+      </c>
+      <c r="D76" t="s">
+        <v>227</v>
+      </c>
+      <c r="E76" t="s">
+        <v>584</v>
+      </c>
+      <c r="F76" t="s">
+        <v>585</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>587</v>
+      </c>
+      <c r="B77" t="s">
+        <v>375</v>
+      </c>
+      <c r="C77" t="s">
+        <v>376</v>
+      </c>
+      <c r="D77" t="s">
+        <v>243</v>
+      </c>
+      <c r="E77" t="s">
+        <v>588</v>
+      </c>
+      <c r="F77" t="s">
+        <v>589</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>591</v>
+      </c>
+      <c r="B78" t="s">
+        <v>592</v>
+      </c>
+      <c r="C78" t="s">
+        <v>593</v>
+      </c>
+      <c r="D78" t="s">
+        <v>255</v>
+      </c>
+      <c r="E78" t="s">
+        <v>594</v>
+      </c>
+      <c r="F78" t="s">
+        <v>595</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>597</v>
+      </c>
+      <c r="B79" t="s">
+        <v>598</v>
+      </c>
+      <c r="C79" t="s">
+        <v>599</v>
+      </c>
+      <c r="D79" t="s">
+        <v>452</v>
+      </c>
+      <c r="E79" t="s">
+        <v>600</v>
+      </c>
+      <c r="F79" t="s">
+        <v>216</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>602</v>
+      </c>
+      <c r="B80" t="s">
+        <v>603</v>
+      </c>
+      <c r="C80" t="s">
+        <v>604</v>
+      </c>
+      <c r="D80" t="s">
+        <v>243</v>
+      </c>
+      <c r="E80" t="s">
+        <v>605</v>
+      </c>
+      <c r="F80" t="s">
+        <v>606</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>608</v>
+      </c>
+      <c r="B81" t="s">
+        <v>603</v>
+      </c>
+      <c r="C81" t="s">
+        <v>604</v>
+      </c>
+      <c r="D81" t="s">
+        <v>243</v>
+      </c>
+      <c r="E81" t="s">
+        <v>605</v>
+      </c>
+      <c r="F81" t="s">
+        <v>606</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>610</v>
+      </c>
+      <c r="B82" t="s">
+        <v>611</v>
+      </c>
+      <c r="C82" t="s">
+        <v>612</v>
+      </c>
+      <c r="D82" t="s">
+        <v>243</v>
+      </c>
+      <c r="E82" t="s">
+        <v>486</v>
+      </c>
+      <c r="F82" t="s">
+        <v>613</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>615</v>
+      </c>
+      <c r="B83" t="s">
+        <v>616</v>
+      </c>
+      <c r="C83" t="s">
+        <v>376</v>
+      </c>
+      <c r="D83" t="s">
+        <v>243</v>
+      </c>
+      <c r="E83" t="s">
+        <v>617</v>
+      </c>
+      <c r="F83" t="s">
+        <v>618</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>620</v>
+      </c>
+      <c r="B84" t="s">
+        <v>621</v>
+      </c>
+      <c r="C84" t="s">
+        <v>400</v>
+      </c>
+      <c r="D84" t="s">
+        <v>243</v>
+      </c>
+      <c r="E84" t="s">
+        <v>622</v>
+      </c>
+      <c r="F84" t="s">
+        <v>623</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>625</v>
+      </c>
+      <c r="B85" t="s">
+        <v>626</v>
+      </c>
+      <c r="C85" t="s">
+        <v>627</v>
+      </c>
+      <c r="D85" t="s">
+        <v>243</v>
+      </c>
+      <c r="E85" t="s">
+        <v>628</v>
+      </c>
+      <c r="F85" t="s">
+        <v>629</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>631</v>
+      </c>
+      <c r="B86" t="s">
+        <v>632</v>
+      </c>
+      <c r="C86" t="s">
+        <v>633</v>
+      </c>
+      <c r="D86" t="s">
+        <v>255</v>
+      </c>
+      <c r="E86" t="s">
+        <v>634</v>
+      </c>
+      <c r="F86" t="s">
+        <v>635</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>637</v>
+      </c>
+      <c r="B87" t="s">
+        <v>638</v>
+      </c>
+      <c r="C87" t="s">
+        <v>221</v>
+      </c>
+      <c r="D87" t="s">
+        <v>243</v>
+      </c>
+      <c r="E87" t="s">
+        <v>297</v>
+      </c>
+      <c r="F87" t="s">
+        <v>639</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>641</v>
+      </c>
+      <c r="B88" t="s">
+        <v>642</v>
+      </c>
+      <c r="C88" t="s">
+        <v>359</v>
+      </c>
+      <c r="D88" t="s">
+        <v>255</v>
+      </c>
+      <c r="E88" t="s">
+        <v>643</v>
+      </c>
+      <c r="F88" t="s">
+        <v>408</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>645</v>
+      </c>
+      <c r="B89" t="s">
+        <v>611</v>
+      </c>
+      <c r="C89" t="s">
+        <v>612</v>
+      </c>
+      <c r="D89" t="s">
+        <v>243</v>
+      </c>
+      <c r="E89" t="s">
+        <v>267</v>
+      </c>
+      <c r="F89" t="s">
+        <v>613</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>647</v>
+      </c>
+      <c r="B90" t="s">
+        <v>648</v>
+      </c>
+      <c r="C90" t="s">
+        <v>649</v>
+      </c>
+      <c r="D90" t="s">
+        <v>243</v>
+      </c>
+      <c r="E90" t="s">
+        <v>650</v>
+      </c>
+      <c r="F90" t="s">
+        <v>651</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>647</v>
+      </c>
+      <c r="B91" t="s">
+        <v>648</v>
+      </c>
+      <c r="C91" t="s">
+        <v>633</v>
+      </c>
+      <c r="D91" t="s">
+        <v>243</v>
+      </c>
+      <c r="E91" t="s">
+        <v>650</v>
+      </c>
+      <c r="F91" t="s">
+        <v>651</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>647</v>
+      </c>
+      <c r="B92" t="s">
+        <v>648</v>
+      </c>
+      <c r="C92" t="s">
+        <v>649</v>
+      </c>
+      <c r="D92" t="s">
+        <v>243</v>
+      </c>
+      <c r="E92" t="s">
+        <v>650</v>
+      </c>
+      <c r="F92" t="s">
+        <v>651</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>655</v>
+      </c>
+      <c r="B93" t="s">
+        <v>656</v>
+      </c>
+      <c r="C93" t="s">
+        <v>221</v>
+      </c>
+      <c r="D93" t="s">
+        <v>227</v>
+      </c>
+      <c r="E93" t="s">
+        <v>657</v>
+      </c>
+      <c r="F93" t="s">
+        <v>216</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>659</v>
+      </c>
+      <c r="B94" t="s">
+        <v>660</v>
+      </c>
+      <c r="C94" t="s">
+        <v>661</v>
+      </c>
+      <c r="D94" t="s">
+        <v>243</v>
+      </c>
+      <c r="E94" t="s">
+        <v>662</v>
+      </c>
+      <c r="F94" t="s">
+        <v>663</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>665</v>
+      </c>
+      <c r="B95" t="s">
+        <v>666</v>
+      </c>
+      <c r="C95" t="s">
+        <v>359</v>
+      </c>
+      <c r="D95" t="s">
+        <v>255</v>
+      </c>
+      <c r="E95" t="s">
+        <v>216</v>
+      </c>
+      <c r="F95" t="s">
+        <v>216</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>668</v>
+      </c>
+      <c r="B96" t="s">
+        <v>669</v>
+      </c>
+      <c r="C96" t="s">
+        <v>221</v>
+      </c>
+      <c r="D96" t="s">
+        <v>234</v>
+      </c>
+      <c r="E96" t="s">
+        <v>670</v>
+      </c>
+      <c r="F96" t="s">
+        <v>671</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>673</v>
+      </c>
+      <c r="B97" t="s">
+        <v>674</v>
+      </c>
+      <c r="C97" t="s">
+        <v>221</v>
+      </c>
+      <c r="D97" t="s">
+        <v>452</v>
+      </c>
+      <c r="E97" t="s">
+        <v>675</v>
+      </c>
+      <c r="F97" t="s">
+        <v>676</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>678</v>
+      </c>
+      <c r="B98" t="s">
+        <v>447</v>
+      </c>
+      <c r="C98" t="s">
+        <v>679</v>
+      </c>
+      <c r="D98" t="s">
+        <v>243</v>
+      </c>
+      <c r="E98" t="s">
+        <v>680</v>
+      </c>
+      <c r="F98" t="s">
+        <v>336</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>682</v>
+      </c>
+      <c r="B99" t="s">
+        <v>447</v>
+      </c>
+      <c r="C99" t="s">
+        <v>679</v>
+      </c>
+      <c r="D99" t="s">
+        <v>243</v>
+      </c>
+      <c r="E99" t="s">
+        <v>680</v>
+      </c>
+      <c r="F99" t="s">
+        <v>336</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>684</v>
+      </c>
+      <c r="B100" t="s">
+        <v>685</v>
+      </c>
+      <c r="C100" t="s">
+        <v>686</v>
+      </c>
+      <c r="D100" t="s">
+        <v>255</v>
+      </c>
+      <c r="E100" t="s">
+        <v>687</v>
+      </c>
+      <c r="F100" t="s">
+        <v>311</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>689</v>
+      </c>
+      <c r="B101" t="s">
+        <v>690</v>
+      </c>
+      <c r="C101" t="s">
+        <v>221</v>
+      </c>
+      <c r="D101" t="s">
+        <v>243</v>
+      </c>
+      <c r="E101" t="s">
+        <v>691</v>
+      </c>
+      <c r="F101" t="s">
+        <v>692</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>694</v>
+      </c>
+      <c r="B102" t="s">
+        <v>685</v>
+      </c>
+      <c r="C102" t="s">
+        <v>686</v>
+      </c>
+      <c r="D102" t="s">
+        <v>255</v>
+      </c>
+      <c r="E102" t="s">
+        <v>695</v>
+      </c>
+      <c r="F102" t="s">
+        <v>311</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>697</v>
+      </c>
+      <c r="B103" t="s">
+        <v>698</v>
+      </c>
+      <c r="C103" t="s">
+        <v>699</v>
+      </c>
+      <c r="D103" t="s">
+        <v>243</v>
+      </c>
+      <c r="E103" t="s">
+        <v>700</v>
+      </c>
+      <c r="F103" t="s">
+        <v>701</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>703</v>
+      </c>
+      <c r="B104" t="s">
+        <v>704</v>
+      </c>
+      <c r="C104" t="s">
+        <v>272</v>
+      </c>
+      <c r="D104" t="s">
+        <v>243</v>
+      </c>
+      <c r="E104" t="s">
+        <v>705</v>
+      </c>
+      <c r="F104" t="s">
+        <v>706</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>708</v>
+      </c>
+      <c r="B105" t="s">
+        <v>709</v>
+      </c>
+      <c r="C105" t="s">
+        <v>710</v>
+      </c>
+      <c r="D105" t="s">
+        <v>243</v>
+      </c>
+      <c r="E105" t="s">
+        <v>711</v>
+      </c>
+      <c r="F105" t="s">
+        <v>216</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>713</v>
+      </c>
+      <c r="B106" t="s">
+        <v>714</v>
+      </c>
+      <c r="C106" t="s">
+        <v>715</v>
+      </c>
+      <c r="D106" t="s">
+        <v>243</v>
+      </c>
+      <c r="E106" t="s">
+        <v>716</v>
+      </c>
+      <c r="F106" t="s">
+        <v>305</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>718</v>
+      </c>
+      <c r="B107" t="s">
+        <v>719</v>
+      </c>
+      <c r="C107" t="s">
+        <v>221</v>
+      </c>
+      <c r="D107" t="s">
+        <v>243</v>
+      </c>
+      <c r="E107" t="s">
+        <v>720</v>
+      </c>
+      <c r="F107" t="s">
+        <v>721</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>723</v>
+      </c>
+      <c r="B108" t="s">
+        <v>724</v>
+      </c>
+      <c r="C108" t="s">
+        <v>725</v>
+      </c>
+      <c r="D108" t="s">
+        <v>243</v>
+      </c>
+      <c r="E108" t="s">
+        <v>726</v>
+      </c>
+      <c r="F108" t="s">
+        <v>727</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>729</v>
+      </c>
+      <c r="B109" t="s">
+        <v>730</v>
+      </c>
+      <c r="C109" t="s">
+        <v>286</v>
+      </c>
+      <c r="D109" t="s">
+        <v>243</v>
+      </c>
+      <c r="E109" t="s">
+        <v>731</v>
+      </c>
+      <c r="F109" t="s">
+        <v>732</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>734</v>
+      </c>
+      <c r="B110" t="s">
+        <v>735</v>
+      </c>
+      <c r="C110" t="s">
+        <v>66</v>
+      </c>
+      <c r="D110" t="s">
+        <v>243</v>
+      </c>
+      <c r="E110" t="s">
+        <v>736</v>
+      </c>
+      <c r="F110" t="s">
+        <v>737</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>739</v>
+      </c>
+      <c r="B111" t="s">
+        <v>740</v>
+      </c>
+      <c r="C111" t="s">
+        <v>376</v>
+      </c>
+      <c r="D111" t="s">
+        <v>243</v>
+      </c>
+      <c r="E111" t="s">
+        <v>741</v>
+      </c>
+      <c r="F111" t="s">
+        <v>742</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>739</v>
+      </c>
+      <c r="B112" t="s">
+        <v>740</v>
+      </c>
+      <c r="C112" t="s">
+        <v>221</v>
+      </c>
+      <c r="D112" t="s">
+        <v>243</v>
+      </c>
+      <c r="E112" t="s">
+        <v>741</v>
+      </c>
+      <c r="F112" t="s">
+        <v>742</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>745</v>
+      </c>
+      <c r="B113" t="s">
+        <v>746</v>
+      </c>
+      <c r="C113" t="s">
+        <v>359</v>
+      </c>
+      <c r="D113" t="s">
+        <v>243</v>
+      </c>
+      <c r="E113" t="s">
+        <v>747</v>
+      </c>
+      <c r="F113" t="s">
+        <v>748</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>750</v>
+      </c>
+      <c r="B114" t="s">
+        <v>730</v>
+      </c>
+      <c r="C114" t="s">
+        <v>286</v>
+      </c>
+      <c r="D114" t="s">
+        <v>243</v>
+      </c>
+      <c r="E114" t="s">
+        <v>751</v>
+      </c>
+      <c r="F114" t="s">
+        <v>732</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>753</v>
+      </c>
+      <c r="B115" t="s">
+        <v>754</v>
+      </c>
+      <c r="C115" t="s">
+        <v>359</v>
+      </c>
+      <c r="D115" t="s">
+        <v>227</v>
+      </c>
+      <c r="E115" t="s">
+        <v>755</v>
+      </c>
+      <c r="F115" t="s">
+        <v>459</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>757</v>
+      </c>
+      <c r="B116" t="s">
+        <v>399</v>
+      </c>
+      <c r="C116" t="s">
+        <v>400</v>
+      </c>
+      <c r="D116" t="s">
+        <v>243</v>
+      </c>
+      <c r="E116" t="s">
+        <v>758</v>
+      </c>
+      <c r="F116" t="s">
+        <v>402</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>760</v>
+      </c>
+      <c r="B117" t="s">
+        <v>754</v>
+      </c>
+      <c r="C117" t="s">
+        <v>359</v>
+      </c>
+      <c r="D117" t="s">
+        <v>227</v>
+      </c>
+      <c r="E117" t="s">
+        <v>761</v>
+      </c>
+      <c r="F117" t="s">
+        <v>459</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>763</v>
+      </c>
+      <c r="B118" t="s">
+        <v>764</v>
+      </c>
+      <c r="C118" t="s">
+        <v>359</v>
+      </c>
+      <c r="D118" t="s">
+        <v>243</v>
+      </c>
+      <c r="E118" t="s">
+        <v>765</v>
+      </c>
+      <c r="F118" t="s">
+        <v>766</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>768</v>
+      </c>
+      <c r="B119" t="s">
+        <v>769</v>
+      </c>
+      <c r="C119" t="s">
+        <v>770</v>
+      </c>
+      <c r="D119" t="s">
+        <v>255</v>
+      </c>
+      <c r="E119" t="s">
+        <v>771</v>
+      </c>
+      <c r="F119" t="s">
+        <v>216</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>773</v>
+      </c>
+      <c r="B120" t="s">
+        <v>774</v>
+      </c>
+      <c r="C120" t="s">
+        <v>309</v>
+      </c>
+      <c r="D120" t="s">
+        <v>243</v>
+      </c>
+      <c r="E120" t="s">
+        <v>775</v>
+      </c>
+      <c r="F120" t="s">
+        <v>776</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>778</v>
+      </c>
+      <c r="B121" t="s">
+        <v>779</v>
+      </c>
+      <c r="C121" t="s">
+        <v>780</v>
+      </c>
+      <c r="D121" t="s">
+        <v>243</v>
+      </c>
+      <c r="E121" t="s">
+        <v>781</v>
+      </c>
+      <c r="F121" t="s">
+        <v>336</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>783</v>
+      </c>
+      <c r="B122" t="s">
+        <v>779</v>
+      </c>
+      <c r="C122" t="s">
+        <v>784</v>
+      </c>
+      <c r="D122" t="s">
+        <v>243</v>
+      </c>
+      <c r="E122" t="s">
+        <v>781</v>
+      </c>
+      <c r="F122" t="s">
+        <v>336</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>786</v>
+      </c>
+      <c r="B123" t="s">
+        <v>779</v>
+      </c>
+      <c r="C123" t="s">
+        <v>787</v>
+      </c>
+      <c r="D123" t="s">
+        <v>243</v>
+      </c>
+      <c r="E123" t="s">
+        <v>781</v>
+      </c>
+      <c r="F123" t="s">
+        <v>336</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>789</v>
+      </c>
+      <c r="B124" t="s">
+        <v>790</v>
+      </c>
+      <c r="C124" t="s">
+        <v>791</v>
+      </c>
+      <c r="D124" t="s">
+        <v>243</v>
+      </c>
+      <c r="E124" t="s">
+        <v>792</v>
+      </c>
+      <c r="F124" t="s">
+        <v>793</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>795</v>
+      </c>
+      <c r="B125" t="s">
+        <v>796</v>
+      </c>
+      <c r="C125" t="s">
+        <v>485</v>
+      </c>
+      <c r="D125" t="s">
+        <v>243</v>
+      </c>
+      <c r="E125" t="s">
+        <v>797</v>
+      </c>
+      <c r="F125" t="s">
+        <v>798</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>800</v>
+      </c>
+      <c r="B126" t="s">
+        <v>375</v>
+      </c>
+      <c r="C126" t="s">
+        <v>376</v>
+      </c>
+      <c r="D126" t="s">
+        <v>243</v>
+      </c>
+      <c r="E126" t="s">
+        <v>801</v>
+      </c>
+      <c r="F126" t="s">
+        <v>216</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>803</v>
+      </c>
+      <c r="B127" t="s">
+        <v>375</v>
+      </c>
+      <c r="C127" t="s">
+        <v>381</v>
+      </c>
+      <c r="D127" t="s">
+        <v>243</v>
+      </c>
+      <c r="E127" t="s">
+        <v>801</v>
+      </c>
+      <c r="F127" t="s">
+        <v>378</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>805</v>
+      </c>
+      <c r="B128" t="s">
+        <v>375</v>
+      </c>
+      <c r="C128" t="s">
+        <v>376</v>
+      </c>
+      <c r="D128" t="s">
+        <v>243</v>
+      </c>
+      <c r="E128" t="s">
+        <v>801</v>
+      </c>
+      <c r="F128" t="s">
+        <v>378</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>807</v>
+      </c>
+      <c r="B129" t="s">
+        <v>375</v>
+      </c>
+      <c r="C129" t="s">
+        <v>808</v>
+      </c>
+      <c r="D129" t="s">
+        <v>243</v>
+      </c>
+      <c r="E129" t="s">
+        <v>801</v>
+      </c>
+      <c r="F129" t="s">
+        <v>378</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>810</v>
+      </c>
+      <c r="B130" t="s">
+        <v>764</v>
+      </c>
+      <c r="C130" t="s">
+        <v>359</v>
+      </c>
+      <c r="D130" t="s">
+        <v>243</v>
+      </c>
+      <c r="E130" t="s">
+        <v>811</v>
+      </c>
+      <c r="F130" t="s">
+        <v>766</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>813</v>
+      </c>
+      <c r="B131" t="s">
+        <v>814</v>
+      </c>
+      <c r="C131" t="s">
+        <v>359</v>
+      </c>
+      <c r="D131" t="s">
+        <v>243</v>
+      </c>
+      <c r="E131" t="s">
+        <v>500</v>
+      </c>
+      <c r="F131" t="s">
+        <v>815</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>817</v>
+      </c>
+      <c r="B132" t="s">
+        <v>632</v>
+      </c>
+      <c r="C132" t="s">
+        <v>633</v>
+      </c>
+      <c r="D132" t="s">
+        <v>255</v>
+      </c>
+      <c r="E132" t="s">
+        <v>818</v>
+      </c>
+      <c r="F132" t="s">
+        <v>819</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>821</v>
+      </c>
+      <c r="B133" t="s">
+        <v>583</v>
+      </c>
+      <c r="C133" t="s">
+        <v>359</v>
+      </c>
+      <c r="D133" t="s">
+        <v>227</v>
+      </c>
+      <c r="E133" t="s">
+        <v>822</v>
+      </c>
+      <c r="F133" t="s">
+        <v>629</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>824</v>
+      </c>
+      <c r="B134" t="s">
+        <v>583</v>
+      </c>
+      <c r="C134" t="s">
+        <v>359</v>
+      </c>
+      <c r="D134" t="s">
+        <v>227</v>
+      </c>
+      <c r="E134" t="s">
+        <v>825</v>
+      </c>
+      <c r="F134" t="s">
+        <v>826</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>828</v>
+      </c>
+      <c r="B135" t="s">
+        <v>829</v>
+      </c>
+      <c r="C135" t="s">
+        <v>830</v>
+      </c>
+      <c r="D135" t="s">
+        <v>255</v>
+      </c>
+      <c r="E135" t="s">
+        <v>526</v>
+      </c>
+      <c r="F135" t="s">
+        <v>831</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>833</v>
+      </c>
+      <c r="B136" t="s">
+        <v>834</v>
+      </c>
+      <c r="C136" t="s">
+        <v>359</v>
+      </c>
+      <c r="D136" t="s">
+        <v>243</v>
+      </c>
+      <c r="E136" t="s">
+        <v>835</v>
+      </c>
+      <c r="F136" t="s">
+        <v>216</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>837</v>
+      </c>
+      <c r="B137" t="s">
+        <v>838</v>
+      </c>
+      <c r="C137" t="s">
+        <v>839</v>
+      </c>
+      <c r="D137" t="s">
+        <v>243</v>
+      </c>
+      <c r="E137" t="s">
+        <v>840</v>
+      </c>
+      <c r="F137" t="s">
+        <v>841</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>843</v>
+      </c>
+      <c r="B138" t="s">
+        <v>844</v>
+      </c>
+      <c r="C138" t="s">
+        <v>845</v>
+      </c>
+      <c r="D138" t="s">
+        <v>234</v>
+      </c>
+      <c r="E138" t="s">
+        <v>846</v>
+      </c>
+      <c r="F138" t="s">
+        <v>847</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>849</v>
+      </c>
+      <c r="B139" t="s">
+        <v>504</v>
+      </c>
+      <c r="C139" t="s">
+        <v>359</v>
+      </c>
+      <c r="D139" t="s">
+        <v>243</v>
+      </c>
+      <c r="E139" t="s">
+        <v>579</v>
+      </c>
+      <c r="F139" t="s">
+        <v>317</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>851</v>
+      </c>
+      <c r="B140" t="s">
+        <v>852</v>
+      </c>
+      <c r="C140" t="s">
+        <v>853</v>
+      </c>
+      <c r="D140" t="s">
+        <v>243</v>
+      </c>
+      <c r="E140" t="s">
+        <v>781</v>
+      </c>
+      <c r="F140" t="s">
+        <v>854</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>856</v>
+      </c>
+      <c r="B141" t="s">
+        <v>857</v>
+      </c>
+      <c r="C141" t="s">
+        <v>858</v>
+      </c>
+      <c r="D141" t="s">
+        <v>243</v>
+      </c>
+      <c r="E141" t="s">
+        <v>859</v>
+      </c>
+      <c r="F141" t="s">
+        <v>860</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>861</v>
       </c>
     </row>
   </sheetData>
@@ -4450,6 +7666,93 @@
     <hyperlink ref="H52" r:id="rId51"/>
     <hyperlink ref="H53" r:id="rId52"/>
     <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4499,554 +7802,554 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>472</v>
+        <v>862</v>
       </c>
       <c r="B2" t="s">
-        <v>473</v>
+        <v>863</v>
       </c>
       <c r="C2" t="s">
-        <v>474</v>
+        <v>864</v>
       </c>
       <c r="D2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F2" t="s">
-        <v>475</v>
+        <v>865</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>476</v>
+        <v>866</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>477</v>
+        <v>867</v>
       </c>
       <c r="B3" t="s">
-        <v>478</v>
+        <v>868</v>
       </c>
       <c r="C3" t="s">
-        <v>479</v>
+        <v>869</v>
       </c>
       <c r="D3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F3" t="s">
-        <v>480</v>
+        <v>870</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>481</v>
+        <v>871</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>482</v>
+        <v>872</v>
       </c>
       <c r="B4" t="s">
-        <v>483</v>
+        <v>873</v>
       </c>
       <c r="C4" t="s">
-        <v>484</v>
+        <v>874</v>
       </c>
       <c r="D4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F4" t="s">
-        <v>485</v>
+        <v>875</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>486</v>
+        <v>876</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>487</v>
+        <v>877</v>
       </c>
       <c r="B5" t="s">
-        <v>488</v>
+        <v>878</v>
       </c>
       <c r="C5" t="s">
-        <v>489</v>
+        <v>879</v>
       </c>
       <c r="D5" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E5" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F5" t="s">
-        <v>475</v>
+        <v>865</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>490</v>
+        <v>880</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>491</v>
+        <v>881</v>
       </c>
       <c r="B6" t="s">
-        <v>492</v>
+        <v>882</v>
       </c>
       <c r="C6" t="s">
-        <v>493</v>
+        <v>883</v>
       </c>
       <c r="D6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F6" t="s">
-        <v>485</v>
+        <v>875</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>494</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>495</v>
+        <v>885</v>
       </c>
       <c r="B7" t="s">
-        <v>496</v>
+        <v>886</v>
       </c>
       <c r="C7" t="s">
-        <v>497</v>
+        <v>887</v>
       </c>
       <c r="D7" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E7" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F7" t="s">
-        <v>480</v>
+        <v>870</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>498</v>
+        <v>888</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>499</v>
+        <v>889</v>
       </c>
       <c r="B8" t="s">
-        <v>500</v>
+        <v>890</v>
       </c>
       <c r="C8" t="s">
-        <v>501</v>
+        <v>891</v>
       </c>
       <c r="D8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F8" t="s">
-        <v>502</v>
+        <v>892</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>503</v>
+        <v>893</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>504</v>
+        <v>894</v>
       </c>
       <c r="B9" t="s">
-        <v>505</v>
+        <v>895</v>
       </c>
       <c r="C9" t="s">
-        <v>506</v>
+        <v>254</v>
       </c>
       <c r="D9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F9" t="s">
-        <v>507</v>
+        <v>896</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>508</v>
+        <v>897</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>509</v>
+        <v>898</v>
       </c>
       <c r="B10" t="s">
-        <v>510</v>
+        <v>899</v>
       </c>
       <c r="C10" t="s">
-        <v>511</v>
+        <v>900</v>
       </c>
       <c r="D10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F10" t="s">
-        <v>502</v>
+        <v>892</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>512</v>
+        <v>901</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>513</v>
+        <v>902</v>
       </c>
       <c r="B11" t="s">
-        <v>514</v>
+        <v>903</v>
       </c>
       <c r="C11" t="s">
-        <v>515</v>
+        <v>904</v>
       </c>
       <c r="D11" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E11" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F11" t="s">
-        <v>485</v>
+        <v>875</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>516</v>
+        <v>905</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>517</v>
+        <v>906</v>
       </c>
       <c r="B12" t="s">
-        <v>518</v>
+        <v>907</v>
       </c>
       <c r="C12" t="s">
-        <v>519</v>
+        <v>908</v>
       </c>
       <c r="D12" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E12" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F12" t="s">
-        <v>485</v>
+        <v>875</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>520</v>
+        <v>909</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>521</v>
+        <v>910</v>
       </c>
       <c r="B13" t="s">
-        <v>522</v>
+        <v>911</v>
       </c>
       <c r="C13" t="s">
-        <v>523</v>
+        <v>912</v>
       </c>
       <c r="D13" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E13" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F13" t="s">
-        <v>273</v>
+        <v>419</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>524</v>
+        <v>913</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>525</v>
+        <v>914</v>
       </c>
       <c r="B14" t="s">
-        <v>492</v>
+        <v>882</v>
       </c>
       <c r="C14" t="s">
-        <v>493</v>
+        <v>883</v>
       </c>
       <c r="D14" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E14" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F14" t="s">
-        <v>485</v>
+        <v>875</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>526</v>
+        <v>915</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>527</v>
+        <v>916</v>
       </c>
       <c r="B15" t="s">
-        <v>528</v>
+        <v>917</v>
       </c>
       <c r="C15" t="s">
-        <v>529</v>
+        <v>918</v>
       </c>
       <c r="D15" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E15" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F15" t="s">
-        <v>485</v>
+        <v>875</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>530</v>
+        <v>919</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>531</v>
+        <v>920</v>
       </c>
       <c r="B16" t="s">
-        <v>532</v>
+        <v>921</v>
       </c>
       <c r="C16" t="s">
-        <v>511</v>
+        <v>900</v>
       </c>
       <c r="D16" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E16" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F16" t="s">
-        <v>533</v>
+        <v>922</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>534</v>
+        <v>923</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>535</v>
+        <v>924</v>
       </c>
       <c r="B17" t="s">
-        <v>536</v>
+        <v>925</v>
       </c>
       <c r="C17" t="s">
-        <v>515</v>
+        <v>904</v>
       </c>
       <c r="D17" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E17" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F17" t="s">
-        <v>502</v>
+        <v>892</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>537</v>
+        <v>926</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>538</v>
+        <v>927</v>
       </c>
       <c r="B18" t="s">
-        <v>539</v>
+        <v>928</v>
       </c>
       <c r="C18" t="s">
-        <v>511</v>
+        <v>900</v>
       </c>
       <c r="D18" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E18" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F18" t="s">
-        <v>502</v>
+        <v>892</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>540</v>
+        <v>929</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>541</v>
+        <v>930</v>
       </c>
       <c r="B19" t="s">
-        <v>542</v>
+        <v>931</v>
       </c>
       <c r="C19" t="s">
-        <v>543</v>
+        <v>932</v>
       </c>
       <c r="D19" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E19" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F19" t="s">
-        <v>485</v>
+        <v>875</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>544</v>
+        <v>933</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>545</v>
+        <v>934</v>
       </c>
       <c r="B20" t="s">
-        <v>492</v>
+        <v>882</v>
       </c>
       <c r="C20" t="s">
-        <v>546</v>
+        <v>935</v>
       </c>
       <c r="D20" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E20" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F20" t="s">
-        <v>485</v>
+        <v>875</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>547</v>
+        <v>936</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>548</v>
+        <v>937</v>
       </c>
       <c r="B21" t="s">
-        <v>549</v>
+        <v>938</v>
       </c>
       <c r="C21" t="s">
-        <v>515</v>
+        <v>904</v>
       </c>
       <c r="D21" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E21" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F21" t="s">
-        <v>485</v>
+        <v>875</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>550</v>
+        <v>939</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>551</v>
+        <v>940</v>
       </c>
       <c r="B22" t="s">
-        <v>552</v>
+        <v>941</v>
       </c>
       <c r="C22" t="s">
-        <v>553</v>
+        <v>942</v>
       </c>
       <c r="D22" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E22" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F22" t="s">
-        <v>485</v>
+        <v>875</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>554</v>
+        <v>943</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>555</v>
+        <v>944</v>
       </c>
       <c r="B23" t="s">
-        <v>556</v>
+        <v>945</v>
       </c>
       <c r="C23" t="s">
-        <v>557</v>
+        <v>946</v>
       </c>
       <c r="D23" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E23" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F23" t="s">
-        <v>485</v>
+        <v>875</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>558</v>
+        <v>947</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>559</v>
+        <v>948</v>
       </c>
       <c r="B24" t="s">
-        <v>560</v>
+        <v>949</v>
       </c>
       <c r="C24" t="s">
-        <v>561</v>
+        <v>950</v>
       </c>
       <c r="D24" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E24" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F24" t="s">
-        <v>485</v>
+        <v>875</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>562</v>
+        <v>951</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>563</v>
+        <v>952</v>
       </c>
       <c r="B25" t="s">
-        <v>564</v>
+        <v>953</v>
       </c>
       <c r="C25" t="s">
-        <v>565</v>
+        <v>954</v>
       </c>
       <c r="D25" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E25" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F25" t="s">
-        <v>485</v>
+        <v>875</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>566</v>
+        <v>955</v>
       </c>
     </row>
   </sheetData>

--- a/docs/xlsx/jobs-2026-08-26.xlsx
+++ b/docs/xlsx/jobs-2026-08-26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="961">
   <si>
     <t>Title</t>
   </si>
@@ -868,21 +868,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/47b0e60abec34fa9b28d4197c8cbd73a-associate-community-organizer-direct-action-research-training-center-olathe</t>
   </si>
   <si>
+    <t>Behavioral Youth Counselor</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Memphis, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4dd706b87dce43de9dbc4e7256ef8f66-behavioral-youth-counselor-youth-villages-memphis</t>
+  </si>
+  <si>
     <t>Behavioral Youth Counselor - Memphis, TN</t>
   </si>
   <si>
-    <t>Youth Villages</t>
-  </si>
-  <si>
     <t>Chicago, Illinois</t>
   </si>
   <si>
-    <t>USD 52000.00 - 60000.00/year</t>
-  </si>
-  <si>
-    <t>Children Youth, Family, Mental Health</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/4dd706b87dce43de9dbc4e7256ef8f66-behavioral-youth-counselor-memphis-tn-youth-villages-chicago</t>
   </si>
   <si>
@@ -901,16 +910,22 @@
     <t>https://www.idealist.org/en/nonprofit-job/a9e013b529944936a56736c0a1075892-bilingual-snap-enrollment-senior-associate-spanish-speaking-project-bread-boston</t>
   </si>
   <si>
+    <t>BLACK RURAL ORGANIZER–IN-TRAINING - Pacific Region (CA, NV, UT, CO, AZ), Northwest Region (NM &amp; WA, OR, ID, MT, WY), &amp; Northern Plains (ND,SD,NE,KS,IA,MN)</t>
+  </si>
+  <si>
+    <t>The Chisholm Legacy Project: A Resource Hub for Black Frontline Climate Justice Leadership</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dcd9471219954628a6ef6f70c022a05f-black-rural-organizerin-training-pacific-region-ca-nv-ut-co-az-northwest-region-nm-wa-or-id-mt-wy-northern-plains-ndsdneksiamn-the-chisholm-legacy-project-a-resource-hub-for-black-frontline-climate-justice-leadership-denver</t>
+  </si>
+  <si>
     <t>BLACK RURAL ORGANIZER–IN-TRAINING - Pacific Region &amp; Northwest Region CA, NV, UT, CO, AZ, NM &amp; WA, OR, ID, MT, WY</t>
-  </si>
-  <si>
-    <t>The Chisholm Legacy Project: A Resource Hub for Black Frontline Climate Justice Leadership</t>
-  </si>
-  <si>
-    <t>USD 50000.00 - 50000.00/year</t>
-  </si>
-  <si>
-    <t>Climate Change, Community Development, Environment</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/dcd9471219954628a6ef6f70c022a05f-black-rural-organizerin-training-pacific-region-northwest-region-ca-nv-ut-co-az-nm-wa-or-id-mt-wy-the-chisholm-legacy-project-a-resource-hub-for-black-frontline-climate-justice-leadership-denver</t>
@@ -4351,7 +4366,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4671,53 +4686,53 @@
         <v>290</v>
       </c>
       <c r="B14" t="s">
+        <v>285</v>
+      </c>
+      <c r="C14" t="s">
         <v>291</v>
       </c>
-      <c r="C14" t="s">
-        <v>272</v>
-      </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
+        <v>287</v>
+      </c>
+      <c r="F14" t="s">
+        <v>288</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="F14" t="s">
-        <v>293</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>293</v>
+      </c>
+      <c r="B15" t="s">
+        <v>294</v>
+      </c>
+      <c r="C15" t="s">
+        <v>272</v>
+      </c>
+      <c r="D15" t="s">
+        <v>243</v>
+      </c>
+      <c r="E15" t="s">
         <v>295</v>
       </c>
-      <c r="B15" t="s">
+      <c r="F15" t="s">
         <v>296</v>
       </c>
-      <c r="C15" t="s">
-        <v>221</v>
-      </c>
-      <c r="D15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="H15" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="F15" t="s">
-        <v>298</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B16" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C16" t="s">
         <v>221</v>
@@ -4726,21 +4741,21 @@
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F16" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B17" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C17" t="s">
         <v>221</v>
@@ -4749,102 +4764,102 @@
         <v>243</v>
       </c>
       <c r="E17" t="s">
+        <v>300</v>
+      </c>
+      <c r="F17" t="s">
+        <v>301</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="F17" t="s">
-        <v>305</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B18" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C18" t="s">
-        <v>309</v>
+        <v>221</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F18" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B19" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C19" t="s">
-        <v>315</v>
+        <v>221</v>
       </c>
       <c r="D19" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="F19" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>312</v>
+      </c>
+      <c r="B20" t="s">
         <v>313</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>314</v>
       </c>
-      <c r="C20" t="s">
-        <v>319</v>
-      </c>
       <c r="D20" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="E20" t="s">
+        <v>315</v>
+      </c>
+      <c r="F20" t="s">
         <v>316</v>
       </c>
-      <c r="F20" t="s">
+      <c r="H20" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>318</v>
+      </c>
+      <c r="B21" t="s">
+        <v>319</v>
+      </c>
+      <c r="C21" t="s">
+        <v>320</v>
+      </c>
+      <c r="D21" t="s">
+        <v>227</v>
+      </c>
+      <c r="E21" t="s">
         <v>321</v>
       </c>
-      <c r="B21" t="s">
-        <v>260</v>
-      </c>
-      <c r="C21" t="s">
-        <v>242</v>
-      </c>
-      <c r="D21" t="s">
-        <v>243</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>322</v>
-      </c>
-      <c r="F21" t="s">
-        <v>262</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>323</v>
@@ -4852,942 +4867,942 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>318</v>
+      </c>
+      <c r="B22" t="s">
+        <v>319</v>
+      </c>
+      <c r="C22" t="s">
         <v>324</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" t="s">
+        <v>227</v>
+      </c>
+      <c r="E22" t="s">
+        <v>321</v>
+      </c>
+      <c r="F22" t="s">
+        <v>322</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="C22" t="s">
-        <v>221</v>
-      </c>
-      <c r="D22" t="s">
-        <v>243</v>
-      </c>
-      <c r="E22" t="s">
-        <v>326</v>
-      </c>
-      <c r="F22" t="s">
-        <v>305</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>326</v>
+      </c>
+      <c r="B23" t="s">
+        <v>260</v>
+      </c>
+      <c r="C23" t="s">
+        <v>242</v>
+      </c>
+      <c r="D23" t="s">
+        <v>243</v>
+      </c>
+      <c r="E23" t="s">
+        <v>327</v>
+      </c>
+      <c r="F23" t="s">
+        <v>262</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="B23" t="s">
-        <v>329</v>
-      </c>
-      <c r="C23" t="s">
-        <v>221</v>
-      </c>
-      <c r="D23" t="s">
-        <v>243</v>
-      </c>
-      <c r="E23" t="s">
-        <v>330</v>
-      </c>
-      <c r="F23" t="s">
-        <v>331</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B24" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C24" t="s">
-        <v>335</v>
+        <v>221</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>244</v>
+        <v>331</v>
       </c>
       <c r="F24" t="s">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B25" t="s">
         <v>334</v>
       </c>
       <c r="C25" t="s">
+        <v>221</v>
+      </c>
+      <c r="D25" t="s">
+        <v>243</v>
+      </c>
+      <c r="E25" t="s">
         <v>335</v>
-      </c>
-      <c r="D25" t="s">
-        <v>243</v>
-      </c>
-      <c r="E25" t="s">
-        <v>244</v>
       </c>
       <c r="F25" t="s">
         <v>336</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>338</v>
+      </c>
+      <c r="B26" t="s">
+        <v>339</v>
+      </c>
+      <c r="C26" t="s">
         <v>340</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" t="s">
+        <v>243</v>
+      </c>
+      <c r="E26" t="s">
+        <v>244</v>
+      </c>
+      <c r="F26" t="s">
         <v>341</v>
       </c>
-      <c r="C26" t="s">
+      <c r="H26" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="D26" t="s">
-        <v>243</v>
-      </c>
-      <c r="E26" t="s">
-        <v>343</v>
-      </c>
-      <c r="F26" t="s">
-        <v>344</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B27" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="C27" t="s">
-        <v>221</v>
+        <v>340</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>348</v>
+        <v>244</v>
       </c>
       <c r="F27" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B28" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C28" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="F28" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B29" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C29" t="s">
-        <v>359</v>
+        <v>221</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="F29" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B30" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C30" t="s">
-        <v>221</v>
+        <v>358</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="F30" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="B31" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C31" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="F31" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B32" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C32" t="s">
-        <v>376</v>
+        <v>221</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="F32" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B33" t="s">
+        <v>374</v>
+      </c>
+      <c r="C33" t="s">
         <v>375</v>
       </c>
-      <c r="C33" t="s">
-        <v>381</v>
-      </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="F33" t="s">
-        <v>216</v>
+        <v>377</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>379</v>
+      </c>
+      <c r="B34" t="s">
+        <v>380</v>
+      </c>
+      <c r="C34" t="s">
+        <v>381</v>
+      </c>
+      <c r="D34" t="s">
+        <v>243</v>
+      </c>
+      <c r="E34" t="s">
+        <v>382</v>
+      </c>
+      <c r="F34" t="s">
+        <v>383</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="B34" t="s">
-        <v>385</v>
-      </c>
-      <c r="C34" t="s">
-        <v>386</v>
-      </c>
-      <c r="D34" t="s">
-        <v>243</v>
-      </c>
-      <c r="E34" t="s">
-        <v>387</v>
-      </c>
-      <c r="F34" t="s">
-        <v>388</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B35" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="C35" t="s">
-        <v>221</v>
+        <v>386</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F35" t="s">
-        <v>393</v>
+        <v>216</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B36" t="s">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="C36" t="s">
-        <v>242</v>
+        <v>391</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F36" t="s">
-        <v>262</v>
+        <v>393</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>395</v>
+      </c>
+      <c r="B37" t="s">
+        <v>396</v>
+      </c>
+      <c r="C37" t="s">
+        <v>221</v>
+      </c>
+      <c r="D37" t="s">
+        <v>243</v>
+      </c>
+      <c r="E37" t="s">
+        <v>397</v>
+      </c>
+      <c r="F37" t="s">
         <v>398</v>
       </c>
-      <c r="B37" t="s">
+      <c r="H37" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="C37" t="s">
-        <v>400</v>
-      </c>
-      <c r="D37" t="s">
-        <v>234</v>
-      </c>
-      <c r="E37" t="s">
-        <v>401</v>
-      </c>
-      <c r="F37" t="s">
-        <v>402</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B38" t="s">
-        <v>405</v>
+        <v>260</v>
       </c>
       <c r="C38" t="s">
-        <v>406</v>
+        <v>242</v>
       </c>
       <c r="D38" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F38" t="s">
-        <v>408</v>
+        <v>262</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B39" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C39" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="D39" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="E39" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="F39" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="B40" t="s">
-        <v>325</v>
+        <v>410</v>
       </c>
       <c r="C40" t="s">
-        <v>221</v>
+        <v>411</v>
       </c>
       <c r="D40" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E40" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="F40" t="s">
-        <v>305</v>
+        <v>413</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>415</v>
+      </c>
+      <c r="B41" t="s">
+        <v>416</v>
+      </c>
+      <c r="C41" t="s">
+        <v>417</v>
+      </c>
+      <c r="D41" t="s">
+        <v>243</v>
+      </c>
+      <c r="E41" t="s">
+        <v>418</v>
+      </c>
+      <c r="F41" t="s">
         <v>419</v>
       </c>
-      <c r="B41" t="s">
+      <c r="H41" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="C41" t="s">
-        <v>421</v>
-      </c>
-      <c r="D41" t="s">
-        <v>243</v>
-      </c>
-      <c r="E41" t="s">
-        <v>422</v>
-      </c>
-      <c r="F41" t="s">
-        <v>423</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B42" t="s">
-        <v>425</v>
+        <v>330</v>
       </c>
       <c r="C42" t="s">
-        <v>426</v>
+        <v>221</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="F42" t="s">
-        <v>428</v>
+        <v>310</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B43" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C43" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D43" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>228</v>
+        <v>427</v>
       </c>
       <c r="F43" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>424</v>
+      </c>
+      <c r="B44" t="s">
+        <v>430</v>
+      </c>
+      <c r="C44" t="s">
+        <v>431</v>
+      </c>
+      <c r="D44" t="s">
+        <v>243</v>
+      </c>
+      <c r="E44" t="s">
+        <v>432</v>
+      </c>
+      <c r="F44" t="s">
+        <v>433</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="B44" t="s">
-        <v>435</v>
-      </c>
-      <c r="C44" t="s">
-        <v>436</v>
-      </c>
-      <c r="D44" t="s">
-        <v>243</v>
-      </c>
-      <c r="E44" t="s">
-        <v>437</v>
-      </c>
-      <c r="F44" t="s">
-        <v>438</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="B45" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C45" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D45" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E45" t="s">
-        <v>443</v>
+        <v>228</v>
       </c>
       <c r="F45" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="C46" t="s">
-        <v>400</v>
+        <v>441</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="F46" t="s">
-        <v>336</v>
+        <v>443</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>445</v>
+      </c>
+      <c r="B47" t="s">
+        <v>446</v>
+      </c>
+      <c r="C47" t="s">
+        <v>447</v>
+      </c>
+      <c r="D47" t="s">
+        <v>243</v>
+      </c>
+      <c r="E47" t="s">
+        <v>448</v>
+      </c>
+      <c r="F47" t="s">
+        <v>449</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="B47" t="s">
-        <v>451</v>
-      </c>
-      <c r="C47" t="s">
-        <v>400</v>
-      </c>
-      <c r="D47" t="s">
-        <v>452</v>
-      </c>
-      <c r="E47" t="s">
-        <v>453</v>
-      </c>
-      <c r="F47" t="s">
-        <v>454</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B48" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C48" t="s">
-        <v>221</v>
+        <v>405</v>
       </c>
       <c r="D48" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="F48" t="s">
-        <v>459</v>
+        <v>341</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="B49" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C49" t="s">
-        <v>242</v>
+        <v>405</v>
       </c>
       <c r="D49" t="s">
-        <v>243</v>
+        <v>457</v>
       </c>
       <c r="E49" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="F49" t="s">
-        <v>216</v>
+        <v>459</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>461</v>
+      </c>
+      <c r="B50" t="s">
+        <v>462</v>
+      </c>
+      <c r="C50" t="s">
+        <v>221</v>
+      </c>
+      <c r="D50" t="s">
+        <v>255</v>
+      </c>
+      <c r="E50" t="s">
+        <v>463</v>
+      </c>
+      <c r="F50" t="s">
+        <v>464</v>
+      </c>
+      <c r="H50" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="B50" t="s">
-        <v>466</v>
-      </c>
-      <c r="C50" t="s">
-        <v>359</v>
-      </c>
-      <c r="D50" t="s">
-        <v>243</v>
-      </c>
-      <c r="E50" t="s">
-        <v>467</v>
-      </c>
-      <c r="F50" t="s">
-        <v>468</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B51" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C51" t="s">
-        <v>472</v>
+        <v>242</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="F51" t="s">
         <v>216</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B52" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C52" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>297</v>
+        <v>472</v>
       </c>
       <c r="F52" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B53" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C53" t="s">
-        <v>221</v>
+        <v>477</v>
       </c>
       <c r="D53" t="s">
         <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F53" t="s">
         <v>216</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>480</v>
+      </c>
+      <c r="B54" t="s">
+        <v>481</v>
+      </c>
+      <c r="C54" t="s">
+        <v>375</v>
+      </c>
+      <c r="D54" t="s">
+        <v>243</v>
+      </c>
+      <c r="E54" t="s">
+        <v>300</v>
+      </c>
+      <c r="F54" t="s">
+        <v>482</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="B54" t="s">
-        <v>484</v>
-      </c>
-      <c r="C54" t="s">
-        <v>485</v>
-      </c>
-      <c r="D54" t="s">
-        <v>243</v>
-      </c>
-      <c r="E54" t="s">
-        <v>486</v>
-      </c>
-      <c r="F54" t="s">
-        <v>487</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B55" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C55" t="s">
-        <v>286</v>
+        <v>221</v>
       </c>
       <c r="D55" t="s">
         <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="F55" t="s">
-        <v>492</v>
+        <v>216</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B56" t="s">
-        <v>375</v>
+        <v>489</v>
       </c>
       <c r="C56" t="s">
-        <v>381</v>
+        <v>490</v>
       </c>
       <c r="D56" t="s">
         <v>243</v>
       </c>
       <c r="E56" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="F56" t="s">
-        <v>378</v>
+        <v>492</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>494</v>
+      </c>
+      <c r="B57" t="s">
+        <v>495</v>
+      </c>
+      <c r="C57" t="s">
+        <v>291</v>
+      </c>
+      <c r="D57" t="s">
+        <v>243</v>
+      </c>
+      <c r="E57" t="s">
+        <v>496</v>
+      </c>
+      <c r="F57" t="s">
         <v>497</v>
       </c>
-      <c r="B57" t="s">
+      <c r="H57" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="C57" t="s">
-        <v>499</v>
-      </c>
-      <c r="D57" t="s">
-        <v>243</v>
-      </c>
-      <c r="E57" t="s">
-        <v>500</v>
-      </c>
-      <c r="F57" t="s">
-        <v>501</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B58" t="s">
-        <v>504</v>
+        <v>380</v>
       </c>
       <c r="C58" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="D58" t="s">
         <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="F58" t="s">
-        <v>506</v>
+        <v>383</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B59" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="C59" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="D59" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="E59" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="F59" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="B60" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C60" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D60" t="s">
         <v>243</v>
       </c>
       <c r="E60" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="F60" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="B61" t="s">
-        <v>260</v>
+        <v>514</v>
       </c>
       <c r="C61" t="s">
-        <v>242</v>
+        <v>515</v>
       </c>
       <c r="D61" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="E61" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F61" t="s">
-        <v>262</v>
+        <v>517</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>519</v>
+      </c>
+      <c r="B62" t="s">
+        <v>520</v>
+      </c>
+      <c r="C62" t="s">
+        <v>364</v>
+      </c>
+      <c r="D62" t="s">
+        <v>243</v>
+      </c>
+      <c r="E62" t="s">
+        <v>521</v>
+      </c>
+      <c r="F62" t="s">
         <v>522</v>
-      </c>
-      <c r="B62" t="s">
-        <v>260</v>
-      </c>
-      <c r="C62" t="s">
-        <v>242</v>
-      </c>
-      <c r="D62" t="s">
-        <v>243</v>
-      </c>
-      <c r="E62" t="s">
-        <v>520</v>
-      </c>
-      <c r="F62" t="s">
-        <v>262</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>523</v>
@@ -5798,418 +5813,418 @@
         <v>524</v>
       </c>
       <c r="B63" t="s">
+        <v>260</v>
+      </c>
+      <c r="C63" t="s">
+        <v>242</v>
+      </c>
+      <c r="D63" t="s">
+        <v>243</v>
+      </c>
+      <c r="E63" t="s">
         <v>525</v>
       </c>
-      <c r="C63" t="s">
-        <v>221</v>
-      </c>
-      <c r="D63" t="s">
-        <v>234</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
+        <v>262</v>
+      </c>
+      <c r="H63" s="2" t="s">
         <v>526</v>
-      </c>
-      <c r="F63" t="s">
-        <v>527</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B64" t="s">
-        <v>504</v>
+        <v>260</v>
       </c>
       <c r="C64" t="s">
-        <v>359</v>
+        <v>242</v>
       </c>
       <c r="D64" t="s">
         <v>243</v>
       </c>
       <c r="E64" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="F64" t="s">
-        <v>531</v>
+        <v>262</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B65" t="s">
-        <v>260</v>
+        <v>530</v>
       </c>
       <c r="C65" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="D65" t="s">
         <v>234</v>
       </c>
       <c r="E65" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F65" t="s">
-        <v>262</v>
+        <v>532</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>534</v>
+      </c>
+      <c r="B66" t="s">
+        <v>509</v>
+      </c>
+      <c r="C66" t="s">
+        <v>364</v>
+      </c>
+      <c r="D66" t="s">
+        <v>243</v>
+      </c>
+      <c r="E66" t="s">
+        <v>535</v>
+      </c>
+      <c r="F66" t="s">
         <v>536</v>
       </c>
-      <c r="B66" t="s">
+      <c r="H66" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="C66" t="s">
-        <v>335</v>
-      </c>
-      <c r="D66" t="s">
-        <v>243</v>
-      </c>
-      <c r="E66" t="s">
-        <v>538</v>
-      </c>
-      <c r="F66" t="s">
-        <v>539</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B67" t="s">
-        <v>375</v>
+        <v>260</v>
       </c>
       <c r="C67" t="s">
-        <v>376</v>
+        <v>242</v>
       </c>
       <c r="D67" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="E67" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F67" t="s">
-        <v>543</v>
+        <v>262</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>541</v>
+      </c>
+      <c r="B68" t="s">
+        <v>542</v>
+      </c>
+      <c r="C68" t="s">
+        <v>340</v>
+      </c>
+      <c r="D68" t="s">
+        <v>243</v>
+      </c>
+      <c r="E68" t="s">
+        <v>543</v>
+      </c>
+      <c r="F68" t="s">
+        <v>544</v>
+      </c>
+      <c r="H68" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="B68" t="s">
-        <v>546</v>
-      </c>
-      <c r="C68" t="s">
-        <v>547</v>
-      </c>
-      <c r="D68" t="s">
-        <v>243</v>
-      </c>
-      <c r="E68" t="s">
-        <v>548</v>
-      </c>
-      <c r="F68" t="s">
-        <v>549</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="B69" t="s">
-        <v>546</v>
+        <v>380</v>
       </c>
       <c r="C69" t="s">
+        <v>381</v>
+      </c>
+      <c r="D69" t="s">
+        <v>243</v>
+      </c>
+      <c r="E69" t="s">
         <v>547</v>
       </c>
-      <c r="D69" t="s">
-        <v>243</v>
-      </c>
-      <c r="E69" t="s">
-        <v>552</v>
-      </c>
       <c r="F69" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>550</v>
+      </c>
+      <c r="B70" t="s">
+        <v>551</v>
+      </c>
+      <c r="C70" t="s">
+        <v>552</v>
+      </c>
+      <c r="D70" t="s">
+        <v>243</v>
+      </c>
+      <c r="E70" t="s">
+        <v>553</v>
+      </c>
+      <c r="F70" t="s">
+        <v>554</v>
+      </c>
+      <c r="H70" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="B70" t="s">
-        <v>556</v>
-      </c>
-      <c r="C70" t="s">
-        <v>557</v>
-      </c>
-      <c r="D70" t="s">
-        <v>243</v>
-      </c>
-      <c r="E70" t="s">
-        <v>558</v>
-      </c>
-      <c r="F70" t="s">
-        <v>559</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B71" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="C71" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="D71" t="s">
         <v>243</v>
       </c>
       <c r="E71" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="F71" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="B72" t="s">
-        <v>504</v>
+        <v>561</v>
       </c>
       <c r="C72" t="s">
-        <v>359</v>
+        <v>562</v>
       </c>
       <c r="D72" t="s">
         <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="F72" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>566</v>
+      </c>
+      <c r="B73" t="s">
+        <v>567</v>
+      </c>
+      <c r="C73" t="s">
+        <v>568</v>
+      </c>
+      <c r="D73" t="s">
+        <v>243</v>
+      </c>
+      <c r="E73" t="s">
+        <v>569</v>
+      </c>
+      <c r="F73" t="s">
+        <v>570</v>
+      </c>
+      <c r="H73" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="B73" t="s">
-        <v>572</v>
-      </c>
-      <c r="C73" t="s">
-        <v>370</v>
-      </c>
-      <c r="D73" t="s">
-        <v>243</v>
-      </c>
-      <c r="E73" t="s">
-        <v>573</v>
-      </c>
-      <c r="F73" t="s">
-        <v>574</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B74" t="s">
-        <v>241</v>
+        <v>509</v>
       </c>
       <c r="C74" t="s">
-        <v>242</v>
+        <v>364</v>
       </c>
       <c r="D74" t="s">
         <v>243</v>
       </c>
       <c r="E74" t="s">
-        <v>244</v>
+        <v>573</v>
       </c>
       <c r="F74" t="s">
-        <v>245</v>
+        <v>574</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>576</v>
+      </c>
+      <c r="B75" t="s">
+        <v>577</v>
+      </c>
+      <c r="C75" t="s">
+        <v>375</v>
+      </c>
+      <c r="D75" t="s">
+        <v>243</v>
+      </c>
+      <c r="E75" t="s">
         <v>578</v>
       </c>
-      <c r="B75" t="s">
-        <v>504</v>
-      </c>
-      <c r="C75" t="s">
-        <v>359</v>
-      </c>
-      <c r="D75" t="s">
-        <v>243</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>579</v>
       </c>
-      <c r="F75" t="s">
+      <c r="H75" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>581</v>
+      </c>
+      <c r="B76" t="s">
+        <v>241</v>
+      </c>
+      <c r="C76" t="s">
+        <v>242</v>
+      </c>
+      <c r="D76" t="s">
+        <v>243</v>
+      </c>
+      <c r="E76" t="s">
+        <v>244</v>
+      </c>
+      <c r="F76" t="s">
+        <v>245</v>
+      </c>
+      <c r="H76" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="B76" t="s">
-        <v>583</v>
-      </c>
-      <c r="C76" t="s">
-        <v>359</v>
-      </c>
-      <c r="D76" t="s">
-        <v>227</v>
-      </c>
-      <c r="E76" t="s">
-        <v>584</v>
-      </c>
-      <c r="F76" t="s">
-        <v>585</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B77" t="s">
-        <v>375</v>
+        <v>509</v>
       </c>
       <c r="C77" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="D77" t="s">
         <v>243</v>
       </c>
       <c r="E77" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="F77" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>587</v>
+      </c>
+      <c r="B78" t="s">
+        <v>588</v>
+      </c>
+      <c r="C78" t="s">
+        <v>364</v>
+      </c>
+      <c r="D78" t="s">
+        <v>227</v>
+      </c>
+      <c r="E78" t="s">
+        <v>589</v>
+      </c>
+      <c r="F78" t="s">
+        <v>590</v>
+      </c>
+      <c r="H78" s="2" t="s">
         <v>591</v>
-      </c>
-      <c r="B78" t="s">
-        <v>592</v>
-      </c>
-      <c r="C78" t="s">
-        <v>593</v>
-      </c>
-      <c r="D78" t="s">
-        <v>255</v>
-      </c>
-      <c r="E78" t="s">
-        <v>594</v>
-      </c>
-      <c r="F78" t="s">
-        <v>595</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="B79" t="s">
-        <v>598</v>
+        <v>380</v>
       </c>
       <c r="C79" t="s">
-        <v>599</v>
+        <v>381</v>
       </c>
       <c r="D79" t="s">
-        <v>452</v>
+        <v>243</v>
       </c>
       <c r="E79" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="F79" t="s">
-        <v>216</v>
+        <v>594</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="B80" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="C80" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="D80" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E80" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="F80" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="B81" t="s">
         <v>603</v>
@@ -6218,289 +6233,289 @@
         <v>604</v>
       </c>
       <c r="D81" t="s">
-        <v>243</v>
+        <v>457</v>
       </c>
       <c r="E81" t="s">
         <v>605</v>
       </c>
       <c r="F81" t="s">
+        <v>216</v>
+      </c>
+      <c r="H81" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>607</v>
+      </c>
+      <c r="B82" t="s">
+        <v>608</v>
+      </c>
+      <c r="C82" t="s">
+        <v>609</v>
+      </c>
+      <c r="D82" t="s">
+        <v>243</v>
+      </c>
+      <c r="E82" t="s">
         <v>610</v>
       </c>
-      <c r="B82" t="s">
+      <c r="F82" t="s">
         <v>611</v>
       </c>
-      <c r="C82" t="s">
+      <c r="H82" s="2" t="s">
         <v>612</v>
-      </c>
-      <c r="D82" t="s">
-        <v>243</v>
-      </c>
-      <c r="E82" t="s">
-        <v>486</v>
-      </c>
-      <c r="F82" t="s">
-        <v>613</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B83" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C83" t="s">
-        <v>376</v>
+        <v>609</v>
       </c>
       <c r="D83" t="s">
         <v>243</v>
       </c>
       <c r="E83" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="F83" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="B84" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C84" t="s">
-        <v>400</v>
+        <v>617</v>
       </c>
       <c r="D84" t="s">
         <v>243</v>
       </c>
       <c r="E84" t="s">
-        <v>622</v>
+        <v>491</v>
       </c>
       <c r="F84" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="B85" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C85" t="s">
-        <v>627</v>
+        <v>381</v>
       </c>
       <c r="D85" t="s">
         <v>243</v>
       </c>
       <c r="E85" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="F85" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="B86" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="C86" t="s">
-        <v>633</v>
+        <v>405</v>
       </c>
       <c r="D86" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E86" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="F86" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="B87" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="C87" t="s">
-        <v>221</v>
+        <v>632</v>
       </c>
       <c r="D87" t="s">
         <v>243</v>
       </c>
       <c r="E87" t="s">
-        <v>297</v>
+        <v>633</v>
       </c>
       <c r="F87" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B88" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C88" t="s">
-        <v>359</v>
+        <v>638</v>
       </c>
       <c r="D88" t="s">
         <v>255</v>
       </c>
       <c r="E88" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="F88" t="s">
-        <v>408</v>
+        <v>640</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>642</v>
+      </c>
+      <c r="B89" t="s">
+        <v>643</v>
+      </c>
+      <c r="C89" t="s">
+        <v>221</v>
+      </c>
+      <c r="D89" t="s">
+        <v>243</v>
+      </c>
+      <c r="E89" t="s">
+        <v>300</v>
+      </c>
+      <c r="F89" t="s">
+        <v>644</v>
+      </c>
+      <c r="H89" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="B89" t="s">
-        <v>611</v>
-      </c>
-      <c r="C89" t="s">
-        <v>612</v>
-      </c>
-      <c r="D89" t="s">
-        <v>243</v>
-      </c>
-      <c r="E89" t="s">
-        <v>267</v>
-      </c>
-      <c r="F89" t="s">
-        <v>613</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>646</v>
+      </c>
+      <c r="B90" t="s">
         <v>647</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
+        <v>364</v>
+      </c>
+      <c r="D90" t="s">
+        <v>255</v>
+      </c>
+      <c r="E90" t="s">
         <v>648</v>
       </c>
-      <c r="C90" t="s">
+      <c r="F90" t="s">
+        <v>413</v>
+      </c>
+      <c r="H90" s="2" t="s">
         <v>649</v>
-      </c>
-      <c r="D90" t="s">
-        <v>243</v>
-      </c>
-      <c r="E90" t="s">
-        <v>650</v>
-      </c>
-      <c r="F90" t="s">
-        <v>651</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B91" t="s">
-        <v>648</v>
+        <v>616</v>
       </c>
       <c r="C91" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="D91" t="s">
         <v>243</v>
       </c>
       <c r="E91" t="s">
-        <v>650</v>
+        <v>267</v>
       </c>
       <c r="F91" t="s">
+        <v>618</v>
+      </c>
+      <c r="H91" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="B92" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="C92" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="D92" t="s">
         <v>243</v>
       </c>
       <c r="E92" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="F92" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>652</v>
+      </c>
+      <c r="B93" t="s">
+        <v>653</v>
+      </c>
+      <c r="C93" t="s">
+        <v>638</v>
+      </c>
+      <c r="D93" t="s">
+        <v>243</v>
+      </c>
+      <c r="E93" t="s">
         <v>655</v>
       </c>
-      <c r="B93" t="s">
+      <c r="F93" t="s">
         <v>656</v>
-      </c>
-      <c r="C93" t="s">
-        <v>221</v>
-      </c>
-      <c r="D93" t="s">
-        <v>227</v>
-      </c>
-      <c r="E93" t="s">
-        <v>657</v>
-      </c>
-      <c r="F93" t="s">
-        <v>216</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>658</v>
@@ -6508,416 +6523,416 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>652</v>
+      </c>
+      <c r="B94" t="s">
+        <v>653</v>
+      </c>
+      <c r="C94" t="s">
+        <v>654</v>
+      </c>
+      <c r="D94" t="s">
+        <v>243</v>
+      </c>
+      <c r="E94" t="s">
+        <v>655</v>
+      </c>
+      <c r="F94" t="s">
+        <v>656</v>
+      </c>
+      <c r="H94" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="B94" t="s">
-        <v>660</v>
-      </c>
-      <c r="C94" t="s">
-        <v>661</v>
-      </c>
-      <c r="D94" t="s">
-        <v>243</v>
-      </c>
-      <c r="E94" t="s">
-        <v>662</v>
-      </c>
-      <c r="F94" t="s">
-        <v>663</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="B95" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="C95" t="s">
-        <v>359</v>
+        <v>221</v>
       </c>
       <c r="D95" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="E95" t="s">
-        <v>216</v>
+        <v>662</v>
       </c>
       <c r="F95" t="s">
         <v>216</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>664</v>
+      </c>
+      <c r="B96" t="s">
+        <v>665</v>
+      </c>
+      <c r="C96" t="s">
+        <v>666</v>
+      </c>
+      <c r="D96" t="s">
+        <v>243</v>
+      </c>
+      <c r="E96" t="s">
+        <v>667</v>
+      </c>
+      <c r="F96" t="s">
         <v>668</v>
       </c>
-      <c r="B96" t="s">
+      <c r="H96" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="C96" t="s">
-        <v>221</v>
-      </c>
-      <c r="D96" t="s">
-        <v>234</v>
-      </c>
-      <c r="E96" t="s">
-        <v>670</v>
-      </c>
-      <c r="F96" t="s">
-        <v>671</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B97" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C97" t="s">
-        <v>221</v>
+        <v>364</v>
       </c>
       <c r="D97" t="s">
-        <v>452</v>
+        <v>255</v>
       </c>
       <c r="E97" t="s">
-        <v>675</v>
+        <v>216</v>
       </c>
       <c r="F97" t="s">
-        <v>676</v>
+        <v>216</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="B98" t="s">
-        <v>447</v>
+        <v>674</v>
       </c>
       <c r="C98" t="s">
-        <v>679</v>
+        <v>221</v>
       </c>
       <c r="D98" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="E98" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="F98" t="s">
-        <v>336</v>
+        <v>676</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B99" t="s">
-        <v>447</v>
+        <v>679</v>
       </c>
       <c r="C99" t="s">
-        <v>679</v>
+        <v>221</v>
       </c>
       <c r="D99" t="s">
-        <v>243</v>
+        <v>457</v>
       </c>
       <c r="E99" t="s">
         <v>680</v>
       </c>
       <c r="F99" t="s">
-        <v>336</v>
+        <v>681</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>683</v>
+      </c>
+      <c r="B100" t="s">
+        <v>452</v>
+      </c>
+      <c r="C100" t="s">
         <v>684</v>
       </c>
-      <c r="B100" t="s">
+      <c r="D100" t="s">
+        <v>243</v>
+      </c>
+      <c r="E100" t="s">
         <v>685</v>
       </c>
-      <c r="C100" t="s">
+      <c r="F100" t="s">
+        <v>341</v>
+      </c>
+      <c r="H100" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="D100" t="s">
-        <v>255</v>
-      </c>
-      <c r="E100" t="s">
-        <v>687</v>
-      </c>
-      <c r="F100" t="s">
-        <v>311</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B101" t="s">
-        <v>690</v>
+        <v>452</v>
       </c>
       <c r="C101" t="s">
-        <v>221</v>
+        <v>684</v>
       </c>
       <c r="D101" t="s">
         <v>243</v>
       </c>
       <c r="E101" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="F101" t="s">
-        <v>692</v>
+        <v>341</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="B102" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="C102" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="D102" t="s">
         <v>255</v>
       </c>
       <c r="E102" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="F102" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>694</v>
+      </c>
+      <c r="B103" t="s">
+        <v>695</v>
+      </c>
+      <c r="C103" t="s">
+        <v>221</v>
+      </c>
+      <c r="D103" t="s">
+        <v>243</v>
+      </c>
+      <c r="E103" t="s">
+        <v>696</v>
+      </c>
+      <c r="F103" t="s">
         <v>697</v>
       </c>
-      <c r="B103" t="s">
+      <c r="H103" s="2" t="s">
         <v>698</v>
-      </c>
-      <c r="C103" t="s">
-        <v>699</v>
-      </c>
-      <c r="D103" t="s">
-        <v>243</v>
-      </c>
-      <c r="E103" t="s">
-        <v>700</v>
-      </c>
-      <c r="F103" t="s">
-        <v>701</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B104" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="C104" t="s">
-        <v>272</v>
+        <v>691</v>
       </c>
       <c r="D104" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E104" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="F104" t="s">
-        <v>706</v>
+        <v>316</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="B105" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="C105" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="D105" t="s">
         <v>243</v>
       </c>
       <c r="E105" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="F105" t="s">
-        <v>216</v>
+        <v>706</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="B106" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C106" t="s">
-        <v>715</v>
+        <v>272</v>
       </c>
       <c r="D106" t="s">
         <v>243</v>
       </c>
       <c r="E106" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="F106" t="s">
-        <v>305</v>
+        <v>711</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="B107" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="C107" t="s">
-        <v>221</v>
+        <v>715</v>
       </c>
       <c r="D107" t="s">
         <v>243</v>
       </c>
       <c r="E107" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="F107" t="s">
-        <v>721</v>
+        <v>216</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="B108" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="C108" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="D108" t="s">
         <v>243</v>
       </c>
       <c r="E108" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="F108" t="s">
-        <v>727</v>
+        <v>310</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="B109" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="C109" t="s">
-        <v>286</v>
+        <v>221</v>
       </c>
       <c r="D109" t="s">
         <v>243</v>
       </c>
       <c r="E109" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F109" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="B110" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="C110" t="s">
-        <v>66</v>
+        <v>730</v>
       </c>
       <c r="D110" t="s">
         <v>243</v>
       </c>
       <c r="E110" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="F110" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="B111" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="C111" t="s">
-        <v>376</v>
+        <v>291</v>
       </c>
       <c r="D111" t="s">
         <v>243</v>
       </c>
       <c r="E111" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="F111" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -6928,7 +6943,7 @@
         <v>740</v>
       </c>
       <c r="C112" t="s">
-        <v>221</v>
+        <v>66</v>
       </c>
       <c r="D112" t="s">
         <v>243</v>
@@ -6940,349 +6955,349 @@
         <v>742</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>744</v>
+      </c>
+      <c r="B113" t="s">
         <v>745</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
+        <v>381</v>
+      </c>
+      <c r="D113" t="s">
+        <v>243</v>
+      </c>
+      <c r="E113" t="s">
         <v>746</v>
       </c>
-      <c r="C113" t="s">
-        <v>359</v>
-      </c>
-      <c r="D113" t="s">
-        <v>243</v>
-      </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
         <v>747</v>
       </c>
-      <c r="F113" t="s">
+      <c r="H113" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="B114" t="s">
-        <v>730</v>
+        <v>745</v>
       </c>
       <c r="C114" t="s">
-        <v>286</v>
+        <v>221</v>
       </c>
       <c r="D114" t="s">
         <v>243</v>
       </c>
       <c r="E114" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="F114" t="s">
-        <v>732</v>
+        <v>747</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>750</v>
+      </c>
+      <c r="B115" t="s">
+        <v>751</v>
+      </c>
+      <c r="C115" t="s">
+        <v>364</v>
+      </c>
+      <c r="D115" t="s">
+        <v>243</v>
+      </c>
+      <c r="E115" t="s">
+        <v>752</v>
+      </c>
+      <c r="F115" t="s">
         <v>753</v>
       </c>
-      <c r="B115" t="s">
+      <c r="H115" s="2" t="s">
         <v>754</v>
-      </c>
-      <c r="C115" t="s">
-        <v>359</v>
-      </c>
-      <c r="D115" t="s">
-        <v>227</v>
-      </c>
-      <c r="E115" t="s">
-        <v>755</v>
-      </c>
-      <c r="F115" t="s">
-        <v>459</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>755</v>
+      </c>
+      <c r="B116" t="s">
+        <v>735</v>
+      </c>
+      <c r="C116" t="s">
+        <v>291</v>
+      </c>
+      <c r="D116" t="s">
+        <v>243</v>
+      </c>
+      <c r="E116" t="s">
+        <v>756</v>
+      </c>
+      <c r="F116" t="s">
+        <v>737</v>
+      </c>
+      <c r="H116" s="2" t="s">
         <v>757</v>
-      </c>
-      <c r="B116" t="s">
-        <v>399</v>
-      </c>
-      <c r="C116" t="s">
-        <v>400</v>
-      </c>
-      <c r="D116" t="s">
-        <v>243</v>
-      </c>
-      <c r="E116" t="s">
-        <v>758</v>
-      </c>
-      <c r="F116" t="s">
-        <v>402</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B117" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="C117" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D117" t="s">
         <v>227</v>
       </c>
       <c r="E117" t="s">
+        <v>760</v>
+      </c>
+      <c r="F117" t="s">
+        <v>464</v>
+      </c>
+      <c r="H117" s="2" t="s">
         <v>761</v>
-      </c>
-      <c r="F117" t="s">
-        <v>459</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>762</v>
+      </c>
+      <c r="B118" t="s">
+        <v>404</v>
+      </c>
+      <c r="C118" t="s">
+        <v>405</v>
+      </c>
+      <c r="D118" t="s">
+        <v>243</v>
+      </c>
+      <c r="E118" t="s">
         <v>763</v>
       </c>
-      <c r="B118" t="s">
+      <c r="F118" t="s">
+        <v>407</v>
+      </c>
+      <c r="H118" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="C118" t="s">
-        <v>359</v>
-      </c>
-      <c r="D118" t="s">
-        <v>243</v>
-      </c>
-      <c r="E118" t="s">
-        <v>765</v>
-      </c>
-      <c r="F118" t="s">
-        <v>766</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B119" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="C119" t="s">
-        <v>770</v>
+        <v>364</v>
       </c>
       <c r="D119" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="E119" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="F119" t="s">
-        <v>216</v>
+        <v>464</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="B120" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C120" t="s">
-        <v>309</v>
+        <v>364</v>
       </c>
       <c r="D120" t="s">
         <v>243</v>
       </c>
       <c r="E120" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="F120" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B121" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="C121" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="D121" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E121" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="F121" t="s">
-        <v>336</v>
+        <v>216</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="B122" t="s">
         <v>779</v>
       </c>
       <c r="C122" t="s">
-        <v>784</v>
+        <v>314</v>
       </c>
       <c r="D122" t="s">
         <v>243</v>
       </c>
       <c r="E122" t="s">
+        <v>780</v>
+      </c>
+      <c r="F122" t="s">
         <v>781</v>
       </c>
-      <c r="F122" t="s">
-        <v>336</v>
-      </c>
       <c r="H122" s="2" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>783</v>
+      </c>
+      <c r="B123" t="s">
+        <v>784</v>
+      </c>
+      <c r="C123" t="s">
+        <v>785</v>
+      </c>
+      <c r="D123" t="s">
+        <v>243</v>
+      </c>
+      <c r="E123" t="s">
         <v>786</v>
       </c>
-      <c r="B123" t="s">
-        <v>779</v>
-      </c>
-      <c r="C123" t="s">
+      <c r="F123" t="s">
+        <v>341</v>
+      </c>
+      <c r="H123" s="2" t="s">
         <v>787</v>
-      </c>
-      <c r="D123" t="s">
-        <v>243</v>
-      </c>
-      <c r="E123" t="s">
-        <v>781</v>
-      </c>
-      <c r="F123" t="s">
-        <v>336</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>788</v>
+      </c>
+      <c r="B124" t="s">
+        <v>784</v>
+      </c>
+      <c r="C124" t="s">
         <v>789</v>
       </c>
-      <c r="B124" t="s">
+      <c r="D124" t="s">
+        <v>243</v>
+      </c>
+      <c r="E124" t="s">
+        <v>786</v>
+      </c>
+      <c r="F124" t="s">
+        <v>341</v>
+      </c>
+      <c r="H124" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="C124" t="s">
-        <v>791</v>
-      </c>
-      <c r="D124" t="s">
-        <v>243</v>
-      </c>
-      <c r="E124" t="s">
-        <v>792</v>
-      </c>
-      <c r="F124" t="s">
-        <v>793</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B125" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="C125" t="s">
-        <v>485</v>
+        <v>792</v>
       </c>
       <c r="D125" t="s">
         <v>243</v>
       </c>
       <c r="E125" t="s">
-        <v>797</v>
+        <v>786</v>
       </c>
       <c r="F125" t="s">
-        <v>798</v>
+        <v>341</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="B126" t="s">
-        <v>375</v>
+        <v>795</v>
       </c>
       <c r="C126" t="s">
-        <v>376</v>
+        <v>796</v>
       </c>
       <c r="D126" t="s">
         <v>243</v>
       </c>
       <c r="E126" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="F126" t="s">
-        <v>216</v>
+        <v>798</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>800</v>
+      </c>
+      <c r="B127" t="s">
+        <v>801</v>
+      </c>
+      <c r="C127" t="s">
+        <v>490</v>
+      </c>
+      <c r="D127" t="s">
+        <v>243</v>
+      </c>
+      <c r="E127" t="s">
+        <v>802</v>
+      </c>
+      <c r="F127" t="s">
         <v>803</v>
-      </c>
-      <c r="B127" t="s">
-        <v>375</v>
-      </c>
-      <c r="C127" t="s">
-        <v>381</v>
-      </c>
-      <c r="D127" t="s">
-        <v>243</v>
-      </c>
-      <c r="E127" t="s">
-        <v>801</v>
-      </c>
-      <c r="F127" t="s">
-        <v>378</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>804</v>
@@ -7293,42 +7308,42 @@
         <v>805</v>
       </c>
       <c r="B128" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C128" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D128" t="s">
         <v>243</v>
       </c>
       <c r="E128" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="F128" t="s">
-        <v>378</v>
+        <v>216</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B129" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C129" t="s">
-        <v>808</v>
+        <v>386</v>
       </c>
       <c r="D129" t="s">
         <v>243</v>
       </c>
       <c r="E129" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="F129" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>809</v>
@@ -7339,275 +7354,321 @@
         <v>810</v>
       </c>
       <c r="B130" t="s">
-        <v>764</v>
+        <v>380</v>
       </c>
       <c r="C130" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="D130" t="s">
         <v>243</v>
       </c>
       <c r="E130" t="s">
+        <v>806</v>
+      </c>
+      <c r="F130" t="s">
+        <v>383</v>
+      </c>
+      <c r="H130" s="2" t="s">
         <v>811</v>
-      </c>
-      <c r="F130" t="s">
-        <v>766</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>812</v>
+      </c>
+      <c r="B131" t="s">
+        <v>380</v>
+      </c>
+      <c r="C131" t="s">
         <v>813</v>
       </c>
-      <c r="B131" t="s">
+      <c r="D131" t="s">
+        <v>243</v>
+      </c>
+      <c r="E131" t="s">
+        <v>806</v>
+      </c>
+      <c r="F131" t="s">
+        <v>383</v>
+      </c>
+      <c r="H131" s="2" t="s">
         <v>814</v>
-      </c>
-      <c r="C131" t="s">
-        <v>359</v>
-      </c>
-      <c r="D131" t="s">
-        <v>243</v>
-      </c>
-      <c r="E131" t="s">
-        <v>500</v>
-      </c>
-      <c r="F131" t="s">
-        <v>815</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>815</v>
+      </c>
+      <c r="B132" t="s">
+        <v>769</v>
+      </c>
+      <c r="C132" t="s">
+        <v>364</v>
+      </c>
+      <c r="D132" t="s">
+        <v>243</v>
+      </c>
+      <c r="E132" t="s">
+        <v>816</v>
+      </c>
+      <c r="F132" t="s">
+        <v>771</v>
+      </c>
+      <c r="H132" s="2" t="s">
         <v>817</v>
-      </c>
-      <c r="B132" t="s">
-        <v>632</v>
-      </c>
-      <c r="C132" t="s">
-        <v>633</v>
-      </c>
-      <c r="D132" t="s">
-        <v>255</v>
-      </c>
-      <c r="E132" t="s">
-        <v>818</v>
-      </c>
-      <c r="F132" t="s">
-        <v>819</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>818</v>
+      </c>
+      <c r="B133" t="s">
+        <v>819</v>
+      </c>
+      <c r="C133" t="s">
+        <v>364</v>
+      </c>
+      <c r="D133" t="s">
+        <v>243</v>
+      </c>
+      <c r="E133" t="s">
+        <v>505</v>
+      </c>
+      <c r="F133" t="s">
+        <v>820</v>
+      </c>
+      <c r="H133" s="2" t="s">
         <v>821</v>
-      </c>
-      <c r="B133" t="s">
-        <v>583</v>
-      </c>
-      <c r="C133" t="s">
-        <v>359</v>
-      </c>
-      <c r="D133" t="s">
-        <v>227</v>
-      </c>
-      <c r="E133" t="s">
-        <v>822</v>
-      </c>
-      <c r="F133" t="s">
-        <v>629</v>
-      </c>
-      <c r="H133" s="2" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>822</v>
+      </c>
+      <c r="B134" t="s">
+        <v>637</v>
+      </c>
+      <c r="C134" t="s">
+        <v>638</v>
+      </c>
+      <c r="D134" t="s">
+        <v>255</v>
+      </c>
+      <c r="E134" t="s">
+        <v>823</v>
+      </c>
+      <c r="F134" t="s">
         <v>824</v>
       </c>
-      <c r="B134" t="s">
-        <v>583</v>
-      </c>
-      <c r="C134" t="s">
-        <v>359</v>
-      </c>
-      <c r="D134" t="s">
-        <v>227</v>
-      </c>
-      <c r="E134" t="s">
+      <c r="H134" s="2" t="s">
         <v>825</v>
-      </c>
-      <c r="F134" t="s">
-        <v>826</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>826</v>
+      </c>
+      <c r="B135" t="s">
+        <v>588</v>
+      </c>
+      <c r="C135" t="s">
+        <v>364</v>
+      </c>
+      <c r="D135" t="s">
+        <v>227</v>
+      </c>
+      <c r="E135" t="s">
+        <v>827</v>
+      </c>
+      <c r="F135" t="s">
+        <v>634</v>
+      </c>
+      <c r="H135" s="2" t="s">
         <v>828</v>
-      </c>
-      <c r="B135" t="s">
-        <v>829</v>
-      </c>
-      <c r="C135" t="s">
-        <v>830</v>
-      </c>
-      <c r="D135" t="s">
-        <v>255</v>
-      </c>
-      <c r="E135" t="s">
-        <v>526</v>
-      </c>
-      <c r="F135" t="s">
-        <v>831</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B136" t="s">
-        <v>834</v>
+        <v>588</v>
       </c>
       <c r="C136" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D136" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="E136" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="F136" t="s">
-        <v>216</v>
+        <v>831</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>833</v>
+      </c>
+      <c r="B137" t="s">
+        <v>834</v>
+      </c>
+      <c r="C137" t="s">
+        <v>835</v>
+      </c>
+      <c r="D137" t="s">
+        <v>255</v>
+      </c>
+      <c r="E137" t="s">
+        <v>531</v>
+      </c>
+      <c r="F137" t="s">
+        <v>836</v>
+      </c>
+      <c r="H137" s="2" t="s">
         <v>837</v>
-      </c>
-      <c r="B137" t="s">
-        <v>838</v>
-      </c>
-      <c r="C137" t="s">
-        <v>839</v>
-      </c>
-      <c r="D137" t="s">
-        <v>243</v>
-      </c>
-      <c r="E137" t="s">
-        <v>840</v>
-      </c>
-      <c r="F137" t="s">
-        <v>841</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="B138" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="C138" t="s">
-        <v>845</v>
+        <v>364</v>
       </c>
       <c r="D138" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E138" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="F138" t="s">
-        <v>847</v>
+        <v>216</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="B139" t="s">
-        <v>504</v>
+        <v>843</v>
       </c>
       <c r="C139" t="s">
-        <v>359</v>
+        <v>844</v>
       </c>
       <c r="D139" t="s">
         <v>243</v>
       </c>
       <c r="E139" t="s">
-        <v>579</v>
+        <v>845</v>
       </c>
       <c r="F139" t="s">
-        <v>317</v>
+        <v>846</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>848</v>
+      </c>
+      <c r="B140" t="s">
+        <v>849</v>
+      </c>
+      <c r="C140" t="s">
+        <v>850</v>
+      </c>
+      <c r="D140" t="s">
+        <v>234</v>
+      </c>
+      <c r="E140" t="s">
         <v>851</v>
       </c>
-      <c r="B140" t="s">
+      <c r="F140" t="s">
         <v>852</v>
       </c>
-      <c r="C140" t="s">
+      <c r="H140" s="2" t="s">
         <v>853</v>
-      </c>
-      <c r="D140" t="s">
-        <v>243</v>
-      </c>
-      <c r="E140" t="s">
-        <v>781</v>
-      </c>
-      <c r="F140" t="s">
-        <v>854</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>854</v>
+      </c>
+      <c r="B141" t="s">
+        <v>509</v>
+      </c>
+      <c r="C141" t="s">
+        <v>364</v>
+      </c>
+      <c r="D141" t="s">
+        <v>243</v>
+      </c>
+      <c r="E141" t="s">
+        <v>584</v>
+      </c>
+      <c r="F141" t="s">
+        <v>322</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>856</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B142" t="s">
         <v>857</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C142" t="s">
         <v>858</v>
       </c>
-      <c r="D141" t="s">
-        <v>243</v>
-      </c>
-      <c r="E141" t="s">
+      <c r="D142" t="s">
+        <v>243</v>
+      </c>
+      <c r="E142" t="s">
+        <v>786</v>
+      </c>
+      <c r="F142" t="s">
         <v>859</v>
       </c>
-      <c r="F141" t="s">
+      <c r="H142" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="H141" s="2" t="s">
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
         <v>861</v>
+      </c>
+      <c r="B143" t="s">
+        <v>862</v>
+      </c>
+      <c r="C143" t="s">
+        <v>863</v>
+      </c>
+      <c r="D143" t="s">
+        <v>243</v>
+      </c>
+      <c r="E143" t="s">
+        <v>864</v>
+      </c>
+      <c r="F143" t="s">
+        <v>865</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>866</v>
       </c>
     </row>
   </sheetData>
@@ -7753,6 +7814,8 @@
     <hyperlink ref="H139" r:id="rId138"/>
     <hyperlink ref="H140" r:id="rId139"/>
     <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -7802,13 +7865,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="B2" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="C2" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="D2" t="s">
         <v>216</v>
@@ -7817,21 +7880,21 @@
         <v>216</v>
       </c>
       <c r="F2" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="B3" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="C3" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="D3" t="s">
         <v>216</v>
@@ -7840,21 +7903,21 @@
         <v>216</v>
       </c>
       <c r="F3" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="B4" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="C4" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="D4" t="s">
         <v>216</v>
@@ -7863,21 +7926,21 @@
         <v>216</v>
       </c>
       <c r="F4" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B5" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="C5" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="D5" t="s">
         <v>216</v>
@@ -7886,21 +7949,21 @@
         <v>216</v>
       </c>
       <c r="F5" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="B6" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="C6" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="D6" t="s">
         <v>216</v>
@@ -7909,21 +7972,21 @@
         <v>216</v>
       </c>
       <c r="F6" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="B7" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="C7" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="D7" t="s">
         <v>216</v>
@@ -7932,21 +7995,21 @@
         <v>216</v>
       </c>
       <c r="F7" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="B8" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="C8" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="D8" t="s">
         <v>216</v>
@@ -7955,18 +8018,18 @@
         <v>216</v>
       </c>
       <c r="F8" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="B9" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C9" t="s">
         <v>254</v>
@@ -7978,21 +8041,21 @@
         <v>216</v>
       </c>
       <c r="F9" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="B10" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="C10" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="D10" t="s">
         <v>216</v>
@@ -8001,21 +8064,21 @@
         <v>216</v>
       </c>
       <c r="F10" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="B11" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="C11" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="D11" t="s">
         <v>216</v>
@@ -8024,21 +8087,21 @@
         <v>216</v>
       </c>
       <c r="F11" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="B12" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="C12" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="D12" t="s">
         <v>216</v>
@@ -8047,21 +8110,21 @@
         <v>216</v>
       </c>
       <c r="F12" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="B13" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="C13" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="D13" t="s">
         <v>216</v>
@@ -8070,21 +8133,21 @@
         <v>216</v>
       </c>
       <c r="F13" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="B14" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="C14" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="D14" t="s">
         <v>216</v>
@@ -8093,21 +8156,21 @@
         <v>216</v>
       </c>
       <c r="F14" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="B15" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="C15" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="D15" t="s">
         <v>216</v>
@@ -8116,21 +8179,21 @@
         <v>216</v>
       </c>
       <c r="F15" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="B16" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="C16" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="D16" t="s">
         <v>216</v>
@@ -8139,21 +8202,21 @@
         <v>216</v>
       </c>
       <c r="F16" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="B17" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="C17" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="D17" t="s">
         <v>216</v>
@@ -8162,21 +8225,21 @@
         <v>216</v>
       </c>
       <c r="F17" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B18" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="C18" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="D18" t="s">
         <v>216</v>
@@ -8185,21 +8248,21 @@
         <v>216</v>
       </c>
       <c r="F18" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="B19" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="C19" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="D19" t="s">
         <v>216</v>
@@ -8208,21 +8271,21 @@
         <v>216</v>
       </c>
       <c r="F19" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="B20" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="C20" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="D20" t="s">
         <v>216</v>
@@ -8231,21 +8294,21 @@
         <v>216</v>
       </c>
       <c r="F20" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="B21" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="C21" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="D21" t="s">
         <v>216</v>
@@ -8254,21 +8317,21 @@
         <v>216</v>
       </c>
       <c r="F21" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="B22" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="C22" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="D22" t="s">
         <v>216</v>
@@ -8277,21 +8340,21 @@
         <v>216</v>
       </c>
       <c r="F22" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="B23" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="C23" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="D23" t="s">
         <v>216</v>
@@ -8300,21 +8363,21 @@
         <v>216</v>
       </c>
       <c r="F23" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="B24" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="C24" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="D24" t="s">
         <v>216</v>
@@ -8323,21 +8386,21 @@
         <v>216</v>
       </c>
       <c r="F24" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="B25" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="C25" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="D25" t="s">
         <v>216</v>
@@ -8346,10 +8409,10 @@
         <v>216</v>
       </c>
       <c r="F25" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
     </row>
   </sheetData>
